--- a/00_Account_Review_Register.xlsx
+++ b/00_Account_Review_Register.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
   <si>
     <t xml:space="preserve">LCC Parks 4090000  —  Account Review Register</t>
   </si>
@@ -85,43 +85,46 @@
     <t xml:space="preserve">AMBER</t>
   </si>
   <si>
-    <t xml:space="preserve">Full account $43,393.37 ex-GST, 36 lines (was partial $1,929.27). Findings: (a) 6 software/subscription lines $1,822.45 belong in 73566 IT Software Licence Fees (Esri, Anthropic, Body2 x2, 2 licence bundles); chart + P10 Canva/VisitUs precedent. (b) 9 of 20 recharge lines $4,416.27 off officer home PK incl confirmed Fry Depots-&gt;Trees miscode and likely AnneMarie/Caroline King mixup. (c) Esri INV000555 tax COMPLIANT (ABN PASS, GST exact, 1 of 7 seats). Body2 L18/L19 = correct monthly recognition of multi-year sub, not duplicates. Bulk Apple lines (L35/L36, $28,843.29) sighted: Exceed ICT INV-13660/INV-17543, ABN 62 633 979 414 PASS, GST exact, reconcile; 18 iPads sub-threshold (P&amp;A advisory).  EVIDENCE/TAX CORRECTION (9-Jun): only 3 external invoices sighted (Esri INV000555, Exceed INV-13660, INV-17543). FIVE external-supply refs NOT sighted/tax-unverified: 2412569490 Single Incident Support (5 lines $522.76), INAU004378 license bundles ($474), GJ076194/GJ075813 Body2 software ($372 each), TE005499 Anthropic ($36.14). Also SEVEN no-attachment recharge lines (not six): adds L20 IJ072790 SR# 201404 $429; total $6,689.87. Tax limb reverts to AMBER.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Finance accept 73564-&gt;73566 software recode $1,822.45 (held); confirm Body2 moved or left. 2 Confirm IT-recharge PK convention (home vs supported-team) for 9 lines. 3 Fry attribution CONFIRMED PK000001 (analyst); both positions map to PK000001. Release net-move 20241/PK000055-&gt;20151/PK000001 on SR-0315517 sighting. 4 Resolve King L08/L24 svc20191/PK000082. 5 Sight 7 no-attach SR backups: SR-0316577, SR-0315241, SR#204868, SR-0312575, SR#201404, SR-0315517, SR#200930 ($6,689.87). 6 Sight + tax-check 5 external invoices: 2412569490, INAU004378, GJ076194, GJ075813, TE005499. 6 Query L34 $3,761.60 quantum. 7 Advisory: P&amp;A register for iPad/iPhone fleet.</t>
+    <t xml:space="preserve">Full account $43,393.37 ex-GST, 36 lines (was partial $1,929.27). Findings: (a) 6 software/subscription lines $1,822.45 belong in 73566 IT Software Licence Fees (Esri, Anthropic, Body2 x2, 2 licence bundles); chart + P10 Canva/VisitUs precedent. (b) 9 of 20 recharge lines $4,416.27 off officer home PK incl confirmed Fry Depots-&gt;Trees miscode and likely AnneMarie/Caroline King mixup. (c) Esri INV000555 tax COMPLIANT (ABN PASS, GST exact, 1 of 7 seats). Body2 L18/L19 = correct monthly recognition of multi-year sub, not duplicates. Bulk Apple lines (L35/L36, $28,843.29) sighted: Exceed ICT INV-13660/INV-17543, ABN 62 633 979 414 PASS, GST exact, reconcile; 18 iPads sub-threshold (P&amp;A advisory).  EVIDENCE/TAX CORRECTION (9-Jun): only 3 external invoices sighted (Esri INV000555, Exceed INV-13660, INV-17543). FIVE external-supply refs NOT sighted/tax-unverified: 2412569490 Single Incident Support (5 lines $522.76), INAU004378 license bundles ($474), GJ076194/GJ075813 Body2 software ($372 each), TE005499 Anthropic ($36.14). Also SEVEN no-attachment recharge lines (not six): adds L20 IJ072790 SR# 201404 $429; total $6,689.87. Tax limb reverts to AMBER. PK ATTRIBUTION (9-Jun): Spero set officer home-PK convention and confirmed 3 of 9 off-home lines: L04 Robertson 20151-&gt;20319 $30, L25 Dressman 20191-&gt;20001 $500, L33 Fry 20241-&gt;20151 $1,929.27 (total $2,459.27), staged as net-moves in recode sub-batch B (nets $0.00). 6 lines remain open ($1,957, mostly Anne-Marie King incl L08/L24 Caroline King name query).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Finance accept 73564-&gt;73566 software recode $1,822.45 (held); confirm Body2 moved or left. 2 Confirm IT-recharge PK convention (home vs supported-team) for 9 lines. 3 Fry attribution CONFIRMED PK000001 (analyst); both positions map to PK000001. Release net-move 20241/PK000055-&gt;20151/PK000001 on SR-0315517 sighting. 4 Resolve King L08/L24 svc20191/PK000082. 5 Sight 7 no-attach SR backups: SR-0316577, SR-0315241, SR#204868, SR-0312575, SR#201404, SR-0315517, SR#200930 ($6,689.87). 6 Sight + tax-check 5 external invoices: 2412569490, INAU004378, GJ076194, GJ075813, TE005499. 6 Query L34 $3,761.60 quantum. 7 Advisory: P&amp;A register for iPad/iPhone fleet. UPDATE 9-Jun: PK convention = officer home PK (Spero); 3 net-moves staged (Robertson/Dressman/Fry); sight SR219175/SR235810/SR-0315517 to clear their evidence limb; 6 King/Shearman lines still pending.</t>
   </si>
   <si>
     <t xml:space="preserve">NA73564_Evidence/ (Esri INV000555 sighted; ledger extract); NA73564_GENJNL_Recode.txt (held)</t>
   </si>
   <si>
+    <t xml:space="preserve">CN-23167 (held: A 73564-&gt;73566 sw; B 3 PK net-moves)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9-Jun-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minor Equipment &amp; Supplies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two overlapping passes (see NA72111 note); account $67,055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GREEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AP-invoice pass: $2,260.36 of $3,433.91 miscoded (Tennyson signage 72222, Ultimate PPE 72113, STIHL GTA 40 72315, INITIATOR chem 72112). Doc46 journal pass recodes $22,028 off 72111 across 11 NAs. The two OVERLAP (Tennyson 27577 $335 in both) and cannot be summed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Resolve TE005091 RED blocker (J12 risers $363.64 double-count vs inv 626529478). 2 Dedupe Doc46 vs AP populations before posting. 3 Carry PPE/STIHL/decal/INITIATOR confirmations to Finance email. See NA72111_Reconciliation_Note.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA72111 note; _CarryForward Doc46/Doc45 source journals</t>
+  </si>
+  <si>
     <t xml:space="preserve">CN-23167 (held)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9-Jun-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minor Equipment &amp; Supplies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two overlapping passes (see NA72111 note); account $67,055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GREEN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AP-invoice pass: $2,260.36 of $3,433.91 miscoded (Tennyson signage 72222, Ultimate PPE 72113, STIHL GTA 40 72315, INITIATOR chem 72112). Doc46 journal pass recodes $22,028 off 72111 across 11 NAs. The two OVERLAP (Tennyson 27577 $335 in both) and cannot be summed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Resolve TE005091 RED blocker (J12 risers $363.64 double-count vs inv 626529478). 2 Dedupe Doc46 vs AP populations before posting. 3 Carry PPE/STIHL/decal/INITIATOR confirmations to Finance email. See NA72111_Reconciliation_Note.md.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA72111 note; _CarryForward Doc46/Doc45 source journals</t>
   </si>
   <si>
     <t xml:space="preserve">72312</t>
@@ -233,10 +236,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="\$#,##0.00"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -391,7 +393,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -436,15 +438,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -857,10 +855,10 @@
       <c r="C6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="6" t="n">
         <v>3433.91</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="6" t="n">
         <v>3777.3</v>
       </c>
       <c r="F6" s="8" t="s">
@@ -888,7 +886,7 @@
         <v>33</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="O6" s="5" t="s">
         <v>25</v>
@@ -896,18 +894,18 @@
     </row>
     <row r="7" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>2461.27</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="6" t="n">
         <v>2707.4</v>
       </c>
       <c r="F7" s="9" t="s">
@@ -926,35 +924,35 @@
         <v>20</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>1021.7</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="6" t="n">
         <v>1123.87</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -973,16 +971,16 @@
         <v>29</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O8" s="5" t="s">
         <v>25</v>
@@ -990,18 +988,18 @@
     </row>
     <row r="9" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="D9" s="6" t="n">
         <v>9495.37</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="6" t="n">
         <v>10444.91</v>
       </c>
       <c r="F9" s="8" t="s">
@@ -1020,16 +1018,16 @@
         <v>20</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="O9" s="5" t="s">
         <v>25</v>
@@ -1037,18 +1035,18 @@
     </row>
     <row r="10" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" s="11" t="n">
+        <v>57</v>
+      </c>
+      <c r="D10" s="6" t="n">
         <v>1059.76</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="6" t="n">
         <v>1165.74</v>
       </c>
       <c r="F10" s="9" t="s">
@@ -1061,22 +1059,22 @@
         <v>20</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>20</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="O10" s="5" t="s">
         <v>25</v>
@@ -1084,18 +1082,18 @@
     </row>
     <row r="11" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" s="11" t="n">
+        <v>64</v>
+      </c>
+      <c r="D11" s="6" t="n">
         <v>3703.03</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="6" t="n">
         <v>4073.33</v>
       </c>
       <c r="F11" s="8" t="s">
@@ -1114,30 +1112,30 @@
         <v>20</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O11" s="5" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C12" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="13" t="n">
+      <c r="C12" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="12" t="n">
         <f aca="false">SUM(D5:D11)</f>
         <v>64568.41</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="12" t="n">
         <f aca="false">SUM(E5:E11)</f>
         <v>71025.26</v>
       </c>

--- a/00_Account_Review_Register.xlsx
+++ b/00_Account_Review_Register.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="71">
   <si>
     <t xml:space="preserve">LCC Parks 4090000  —  Account Review Register</t>
   </si>
@@ -115,34 +115,37 @@
     <t xml:space="preserve">RED</t>
   </si>
   <si>
-    <t xml:space="preserve">AP-invoice pass: $2,260.36 of $3,433.91 miscoded (Tennyson signage 72222, Ultimate PPE 72113, STIHL GTA 40 72315, INITIATOR chem 72112). Doc46 journal pass recodes $22,028 off 72111 across 11 NAs. The two OVERLAP (Tennyson 27577 $335 in both) and cannot be summed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Resolve TE005091 RED blocker (J12 risers $363.64 double-count vs inv 626529478). 2 Dedupe Doc46 vs AP populations before posting. 3 Carry PPE/STIHL/decal/INITIATOR confirmations to Finance email. See NA72111_Reconciliation_Note.md.</t>
+    <t xml:space="preserve">AP-invoice pass: $2,260.36 of $3,433.91 miscoded (Tennyson signage 72222, Ultimate PPE 72113, STIHL GTA 40 72315, INITIATOR chem 72112). Doc46 journal pass recodes $22,028 off 72111 across 11 NAs. The two OVERLAP (Tennyson 27577 $335 in both) and cannot be summed. EVIDENCE SIGHTED 9-Jun (Ultimate/Woodmans/Tennyson set C00267478, all ABNs PASS): 3 Trees-PK (20241/PK000055) recodes now STAGED in NA72111_GENJNL_Recode.txt - trousers PIK2270125 $292.09 and pants PIK2267644 $402.59 to 72113 PPE (partial, off mixed invoices), STIHL GTA 40 PIK2267816 $439.68 to 72315 parks P&amp;A (full); nets $0.00. Tennyson 27577 $335 evidence sighted, 72222 recode still HELD (Doc46 dedup). Woodmans 6429672 $54.41 correct in 72111.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Resolve TE005091 RED blocker (J12 risers $363.64 double-count vs inv 626529478). 2 Dedupe Doc46 vs AP populations before posting. 3 Carry PPE/STIHL/decal/INITIATOR confirmations to Finance email. See NA72111_Reconciliation_Note.md. UPDATE 9-Jun: PPE destination set to 72113 by Spero; 3 recodes staged; STIHL and PPE/decal evidence gaps closed. Still open: TE005091 dedup, Doc46-vs-AP population match, untested remainder.</t>
   </si>
   <si>
     <t xml:space="preserve">NA72111 note; _CarryForward Doc46/Doc45 source journals</t>
   </si>
   <si>
+    <t xml:space="preserve">CN-23167 (held; NA72111_GENJNL_Recode.txt 3 lines)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">72312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office &amp; Library Equipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IKEA PK000493 svc20392 (PCard) + Empire PK000001 svc20151 (AP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$2,461.27 of $2,461.27 (100%) miscoded out of 72312; IKEA EKET cabinets and Empire chair gas lifts + desk power + install all belong in 72313 Furniture &amp; Fittings. IKEA line PK000493 CONFIRMED valid (Flying Gang, Park Services, svc 20392) per analyst sub-PK ledger; PK preserved as transacted, no PK move. Both ABNs checksum PASS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Finance accept 72312 to 72313 recode in full-reversal format, then release CN-23167. 2 CAVEAT: pk_validator fails PK000493 (absent from installed maps which carry only PK000022 for svc 20392); add the Flying Gang sub-PK to lcc-coding-review so the recode validates. 3 Advisory: fix line 02 narration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA72312_Evidence/ (IKEA TE004431; Empire RL196475; ledger extract)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CN-23167 (held)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Office &amp; Library Equipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IKEA PK000493 svc20392 (PCard) + Empire PK000001 svc20151 (AP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$2,461.27 of $2,461.27 (100%) miscoded out of 72312; IKEA EKET cabinets and Empire chair gas lifts + desk power + install all belong in 72313 Furniture &amp; Fittings. IKEA line PK000493 CONFIRMED valid (Flying Gang, Park Services, svc 20392) per analyst sub-PK ledger; PK preserved as transacted, no PK move. Both ABNs checksum PASS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Finance accept 72312 to 72313 recode in full-reversal format, then release CN-23167. 2 CAVEAT: pk_validator fails PK000493 (absent from installed maps which carry only PK000022 for svc 20392); add the Flying Gang sub-PK to lcc-coding-review so the recode validates. 3 Advisory: fix line 02 narration.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA72312_Evidence/ (IKEA TE004431; Empire RL196475; ledger extract)</t>
   </si>
   <si>
     <t xml:space="preserve">8-Jun-2026</t>
@@ -933,21 +936,21 @@
         <v>40</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>1021.7</v>
@@ -971,16 +974,16 @@
         <v>29</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O8" s="5" t="s">
         <v>25</v>
@@ -988,13 +991,13 @@
     </row>
     <row r="9" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>9495.37</v>
@@ -1018,16 +1021,16 @@
         <v>20</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="O9" s="5" t="s">
         <v>25</v>
@@ -1035,13 +1038,13 @@
     </row>
     <row r="10" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>1059.76</v>
@@ -1059,22 +1062,22 @@
         <v>20</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>20</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="O10" s="5" t="s">
         <v>25</v>
@@ -1082,13 +1085,13 @@
     </row>
     <row r="11" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>3703.03</v>
@@ -1112,16 +1115,16 @@
         <v>20</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="O11" s="5" t="s">
         <v>25</v>
@@ -1129,7 +1132,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C12" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" s="12" t="n">
         <f aca="false">SUM(D5:D11)</f>

--- a/00_Account_Review_Register.xlsx
+++ b/00_Account_Review_Register.xlsx
@@ -115,7 +115,7 @@
     <t xml:space="preserve">RED</t>
   </si>
   <si>
-    <t xml:space="preserve">AP-invoice pass: $2,260.36 of $3,433.91 miscoded (Tennyson signage 72222, Ultimate PPE 72113, STIHL GTA 40 72315, INITIATOR chem 72112). Doc46 journal pass recodes $22,028 off 72111 across 11 NAs. The two OVERLAP (Tennyson 27577 $335 in both) and cannot be summed. EVIDENCE SIGHTED 9-Jun (Ultimate/Woodmans/Tennyson set C00267478, all ABNs PASS): 3 Trees-PK (20241/PK000055) recodes now STAGED in NA72111_GENJNL_Recode.txt - trousers PIK2270125 $292.09 and pants PIK2267644 $402.59 to 72113 PPE (partial, off mixed invoices), STIHL GTA 40 PIK2267816 $439.68 to 72315 parks P&amp;A (full); nets $0.00. Tennyson 27577 $335 evidence sighted, 72222 recode still HELD (Doc46 dedup). Woodmans 6429672 $54.41 correct in 72111.</t>
+    <t xml:space="preserve">AP-invoice pass: $2,260.36 of $3,433.91 miscoded (Tennyson signage 72222, Ultimate PPE 72113, STIHL GTA 40 72315, INITIATOR chem 72112). Doc46 journal pass recodes $22,028 off 72111 across 11 NAs. The two OVERLAP (Tennyson 27577 $335 in both) and cannot be summed. EVIDENCE SIGHTED 9-Jun (Ultimate/Woodmans/Tennyson set C00267478, all ABNs PASS): 3 Trees-PK (20241/PK000055) recodes now STAGED in NA72111_GENJNL_Recode.txt - trousers PIK2270125 $292.09 and pants PIK2267644 $402.59 to 72113 PPE (partial, off mixed invoices), STIHL GTA 40 PIK2267816 $439.68 to 72315 parks P&amp;A (full); nets $0.00. Tennyson 27577 $335 evidence sighted, 72222 recode still HELD (Doc46 dedup). Woodmans 6429672 $54.41 correct in 72111. SET 2 staged 9-Jun (Motorcycles R Us PPE, svc 20301/PK000084, Spero directive): doc10286878 4 items $883.49 partial + doc10287279 pants $179.95 full = $1,063.44 ex to 72113. EVIDENCE GAP: Moto R Us invoices not packaged, ABN/GST unverified. Combined 72111 recode now $2,197.80 out ($1,758.12 to 72113, $439.68 to 72315), nets $0.00.</t>
   </si>
   <si>
     <t xml:space="preserve">1 Resolve TE005091 RED blocker (J12 risers $363.64 double-count vs inv 626529478). 2 Dedupe Doc46 vs AP populations before posting. 3 Carry PPE/STIHL/decal/INITIATOR confirmations to Finance email. See NA72111_Reconciliation_Note.md. UPDATE 9-Jun: PPE destination set to 72113 by Spero; 3 recodes staged; STIHL and PPE/decal evidence gaps closed. Still open: TE005091 dedup, Doc46-vs-AP population match, untested remainder.</t>
@@ -124,7 +124,7 @@
     <t xml:space="preserve">NA72111 note; _CarryForward Doc46/Doc45 source journals</t>
   </si>
   <si>
-    <t xml:space="preserve">CN-23167 (held; NA72111_GENJNL_Recode.txt 3 lines)</t>
+    <t xml:space="preserve">CN-23167 (held; NA72111_GENJNL_Recode.txt 10 lines, 2 sets)</t>
   </si>
   <si>
     <t xml:space="preserve">72312</t>

--- a/00_Account_Review_Register.xlsx
+++ b/00_Account_Review_Register.xlsx
@@ -115,7 +115,7 @@
     <t xml:space="preserve">RED</t>
   </si>
   <si>
-    <t xml:space="preserve">AP-invoice pass: $2,260.36 of $3,433.91 miscoded (Tennyson signage 72222, Ultimate PPE 72113, STIHL GTA 40 72315, INITIATOR chem 72112). Doc46 journal pass recodes $22,028 off 72111 across 11 NAs. The two OVERLAP (Tennyson 27577 $335 in both) and cannot be summed. EVIDENCE SIGHTED 9-Jun (Ultimate/Woodmans/Tennyson set C00267478, all ABNs PASS): 3 Trees-PK (20241/PK000055) recodes now STAGED in NA72111_GENJNL_Recode.txt - trousers PIK2270125 $292.09 and pants PIK2267644 $402.59 to 72113 PPE (partial, off mixed invoices), STIHL GTA 40 PIK2267816 $439.68 to 72315 parks P&amp;A (full); nets $0.00. Tennyson 27577 $335 evidence sighted, 72222 recode still HELD (Doc46 dedup). Woodmans 6429672 $54.41 correct in 72111. SET 2 staged 9-Jun (Motorcycles R Us PPE, svc 20301/PK000084, Spero directive): doc10286878 4 items $883.49 partial + doc10287279 pants $179.95 full = $1,063.44 ex to 72113. EVIDENCE GAP: Moto R Us invoices not packaged, ABN/GST unverified. Combined 72111 recode now $2,197.80 out ($1,758.12 to 72113, $439.68 to 72315), nets $0.00.</t>
+    <t xml:space="preserve">AP-invoice pass: $2,260.36 of $3,433.91 miscoded (Tennyson signage 72222, Ultimate PPE 72113, STIHL GTA 40 72315, INITIATOR chem 72112). Doc46 journal pass recodes $22,028 off 72111 across 11 NAs. The two OVERLAP (Tennyson 27577 $335 in both) and cannot be summed. EVIDENCE SIGHTED 9-Jun (Ultimate/Woodmans/Tennyson set C00267478, all ABNs PASS): 3 Trees-PK (20241/PK000055) recodes now STAGED in NA72111_GENJNL_Recode.txt - trousers PIK2270125 $292.09 and pants PIK2267644 $402.59 to 72113 PPE (partial, off mixed invoices), STIHL GTA 40 PIK2267816 $439.68 to 72315 parks P&amp;A (full); nets $0.00. Tennyson 27577 $335 evidence sighted, 72222 recode still HELD (Doc46 dedup). Woodmans 6429672 $54.41 correct in 72111. SET 2 staged 9-Jun (Motorcycles R Us PPE, svc 20301/PK000084, Spero directive): doc10286878 4 items $883.49 partial + doc10287279 pants $179.95 full = $1,063.44 ex to 72113. EVIDENCE GAP: Moto R Us invoices not packaged, ABN/GST unverified. Combined 72111 recode now $2,197.80 out ($1,758.12 to 72113, $439.68 to 72315), nets $0.00. SET 3 staged 9-Jun (scrap-plaque income reclass, Spero directive): -$448.00 ex "returned plaques for scrap" (SC10906) is sale income miscoded as a credit in 72111 expense on Depots PK000001; reclass to 64411 Sale of materials (revenue, unrestricted) on Cemeteries svc 20451/PK000402. Income reclass, signs inverted (Dr 72111 +448, Cr 64411 -448). Source doc SC10906 not sighted. Combined 72111 recode now 12 lines, net 72111 movement -$1,749.80, batch nets $0.00.</t>
   </si>
   <si>
     <t xml:space="preserve">1 Resolve TE005091 RED blocker (J12 risers $363.64 double-count vs inv 626529478). 2 Dedupe Doc46 vs AP populations before posting. 3 Carry PPE/STIHL/decal/INITIATOR confirmations to Finance email. See NA72111_Reconciliation_Note.md. UPDATE 9-Jun: PPE destination set to 72113 by Spero; 3 recodes staged; STIHL and PPE/decal evidence gaps closed. Still open: TE005091 dedup, Doc46-vs-AP population match, untested remainder.</t>
@@ -124,7 +124,7 @@
     <t xml:space="preserve">NA72111 note; _CarryForward Doc46/Doc45 source journals</t>
   </si>
   <si>
-    <t xml:space="preserve">CN-23167 (held; NA72111_GENJNL_Recode.txt 10 lines, 2 sets)</t>
+    <t xml:space="preserve">CN-23167 (held; NA72111_GENJNL_Recode.txt 12 lines, 3 sets)</t>
   </si>
   <si>
     <t xml:space="preserve">72312</t>

--- a/00_Account_Review_Register.xlsx
+++ b/00_Account_Review_Register.xlsx
@@ -94,7 +94,7 @@
     <t xml:space="preserve">NA73564_Evidence/ (Esri INV000555 sighted; ledger extract); NA73564_GENJNL_Recode.txt (held)</t>
   </si>
   <si>
-    <t xml:space="preserve">CN-23167 (held: A 73564-&gt;73566 sw; B 3 PK net-moves)</t>
+    <t xml:space="preserve">CN-23167 (A 73564-&gt;73566 HELD-Finance; B 3 PK net-moves PREPARED per directive)</t>
   </si>
   <si>
     <t xml:space="preserve">9-Jun-2026</t>
@@ -115,7 +115,7 @@
     <t xml:space="preserve">RED</t>
   </si>
   <si>
-    <t xml:space="preserve">AP-invoice pass: $2,260.36 of $3,433.91 miscoded (Tennyson signage 72222, Ultimate PPE 72113, STIHL GTA 40 72315, INITIATOR chem 72112). Doc46 journal pass recodes $22,028 off 72111 across 11 NAs. The two OVERLAP (Tennyson 27577 $335 in both) and cannot be summed. EVIDENCE SIGHTED 9-Jun (Ultimate/Woodmans/Tennyson set C00267478, all ABNs PASS): 3 Trees-PK (20241/PK000055) recodes now STAGED in NA72111_GENJNL_Recode.txt - trousers PIK2270125 $292.09 and pants PIK2267644 $402.59 to 72113 PPE (partial, off mixed invoices), STIHL GTA 40 PIK2267816 $439.68 to 72315 parks P&amp;A (full); nets $0.00. Tennyson 27577 $335 evidence sighted, 72222 recode still HELD (Doc46 dedup). Woodmans 6429672 $54.41 correct in 72111. SET 2 staged 9-Jun (Motorcycles R Us PPE, svc 20301/PK000084, Spero directive): doc10286878 4 items $883.49 partial + doc10287279 pants $179.95 full = $1,063.44 ex to 72113. EVIDENCE GAP: Moto R Us invoices not packaged, ABN/GST unverified. Combined 72111 recode now $2,197.80 out ($1,758.12 to 72113, $439.68 to 72315), nets $0.00. SET 3 staged 9-Jun (scrap-plaque income reclass, Spero directive): -$448.00 ex "returned plaques for scrap" (SC10906) is sale income miscoded as a credit in 72111 expense on Depots PK000001; reclass to 64411 Sale of materials (revenue, unrestricted) on Cemeteries svc 20451/PK000402. Income reclass, signs inverted (Dr 72111 +448, Cr 64411 -448). Source doc SC10906 not sighted. Combined 72111 recode now 12 lines, net 72111 movement -$1,749.80, batch nets $0.00.</t>
+    <t xml:space="preserve">AP-invoice pass: $2,260.36 of $3,433.91 miscoded (Tennyson signage 72222, Ultimate PPE 72113, STIHL GTA 40 72315, INITIATOR chem 72112). Doc46 journal pass recodes $22,028 off 72111 across 11 NAs. The two OVERLAP (Tennyson 27577 $335 in both) and cannot be summed. EVIDENCE SIGHTED 9-Jun (Ultimate/Woodmans/Tennyson set C00267478, all ABNs PASS): 3 Trees-PK (20241/PK000055) recodes now STAGED in NA72111_GENJNL_Recode.txt - trousers PIK2270125 $292.09 and pants PIK2267644 $402.59 to 72113 PPE (partial, off mixed invoices), STIHL GTA 40 PIK2267816 $439.68 to 72315 parks P&amp;A (full); nets $0.00. Tennyson 27577 $335 evidence sighted, 72222 recode still HELD (Doc46 dedup). Woodmans 6429672 $54.41 correct in 72111. SET 2 staged 9-Jun (Motorcycles R Us PPE, svc 20301/PK000084, Spero directive): doc10286878 4 items $883.49 partial + doc10287279 pants $179.95 full = $1,063.44 ex to 72113. EVIDENCE GAP: Moto R Us invoices not packaged, ABN/GST unverified. Combined 72111 recode now $2,197.80 out ($1,758.12 to 72113, $439.68 to 72315), nets $0.00. SET 3 staged 9-Jun (scrap-plaque income reclass, Spero directive): -$448.00 ex "returned plaques for scrap" (SC10906) is sale income miscoded as a credit in 72111 expense on Depots PK000001; reclass to 64411 Sale of materials (revenue, unrestricted) on Cemeteries svc 20451/PK000402. Income reclass, signs inverted (Dr 72111 +448, Cr 64411 -448). Source doc SC10906 not sighted. Combined 72111 recode now 12 lines, net 72111 movement -$1,749.80, batch nets $0.00. SET 4 + DIRECTIVE 9-Jun: Spero standing directive - instructed lines override criteria and are PREPARED FOR JOURNAL (source-doc gaps audit-noted, not blocking). Set 4: TE004824 Officeworks 624206983 (ABN PASS, sighted) Posca PC5M markers $41.05 ex to 73563 stationery. 14-line recode now PREPARED; net 72111 -$1,790.85, nets $0.00 (72113 +1758.12, 72315 +439.68, 73563 +41.05, 64411 -448.00). Advisory: 3 OTTO desk risers $54.52 ex = 72313 candidate, not journalled pending instruction.</t>
   </si>
   <si>
     <t xml:space="preserve">1 Resolve TE005091 RED blocker (J12 risers $363.64 double-count vs inv 626529478). 2 Dedupe Doc46 vs AP populations before posting. 3 Carry PPE/STIHL/decal/INITIATOR confirmations to Finance email. See NA72111_Reconciliation_Note.md. UPDATE 9-Jun: PPE destination set to 72113 by Spero; 3 recodes staged; STIHL and PPE/decal evidence gaps closed. Still open: TE005091 dedup, Doc46-vs-AP population match, untested remainder.</t>
@@ -124,7 +124,7 @@
     <t xml:space="preserve">NA72111 note; _CarryForward Doc46/Doc45 source journals</t>
   </si>
   <si>
-    <t xml:space="preserve">CN-23167 (held; NA72111_GENJNL_Recode.txt 12 lines, 3 sets)</t>
+    <t xml:space="preserve">CN-23167 (PREPARED; NA72111_GENJNL_Recode.txt 14 lines, 4 sets)</t>
   </si>
   <si>
     <t xml:space="preserve">72312</t>

--- a/00_Account_Review_Register.xlsx
+++ b/00_Account_Review_Register.xlsx
@@ -181,13 +181,13 @@
     <t xml:space="preserve">PK000001 svc20151 + PK000086 svc20141 + PK000082 svc20191</t>
   </si>
   <si>
-    <t xml:space="preserve">$6,354.47 of $9,495.37 (66.9%) miscoded out of 73563. [Recode sign-corrected 9-Jun: P1-P10 PK000001 PPE pair direction fixed; was $6,307.33.] Catch-all WINC stationery order used for tearoom, IT, cleaning, batteries, chemical, PPE. Feb WINC 9901763737 ($1,240.45) and Officeworks TE005250 ($352.73) NOW SIGHTED; both follow the same pattern. WINC ABN &amp; Officeworks ABN checksum PASS. EVIDENCE CORRECTION (9-Jun): only 2 of 11 WINC line-detail invoices sighted (9901763737 Feb, 9901782965 April). The P1-P10 audit is derived analysis, not primary evidence. NINE WINC invoices NOT sighted: 9901690129, 9901699602, 9901709054, 9901718415, 9901727996, 9901737473, 9901746332, 9901754676, 9901773647. Evidence limb reverts to AMBER.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Confirm Finance accepts WINC systemic recode out of 73563. 2 Confirm TE005250 desk risers 72313 vs 72111. 3 Confirm 73512 movements Reason B (filter 50/50). 4 Release CN-23167. + Sight the 9 unsighted WINC source invoices (9901690129, 9901699602, 9901709054, 9901718415, 9901727996, 9901737473, 9901746332, 9901754676, 9901773647) for line-level support of the recode.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA73563_Evidence/ (WINC P1-P10 audit, April, Feb, Officeworks 628185694, recon, ledger)</t>
+    <t xml:space="preserve">$6,354.47 of $9,495.37 (66.9%) miscoded out of 73563. [Recode sign-corrected 9-Jun: P1-P10 PK000001 PPE pair direction fixed; was $6,307.33.] Catch-all WINC stationery order used for tearoom, IT, cleaning, batteries, chemical, PPE. Feb WINC 9901763737 ($1,240.45) and Officeworks TE005250 ($352.73) NOW SIGHTED; both follow the same pattern. WINC ABN &amp; Officeworks ABN checksum PASS. EVIDENCE CORRECTION (9-Jun): only 2 of 11 WINC line-detail invoices sighted (9901763737 Feb, 9901782965 April). The P1-P10 audit is derived analysis, not primary evidence. NINE WINC invoices NOT sighted: 9901690129, 9901699602, 9901709054, 9901718415, 9901727996, 9901737473, 9901746332, 9901754676, 9901773647. Evidence limb reverts to AMBER. EVIDENCE CLOSED 9-Jun: the nine unsighted WINC invoices recovered from the _CarryForward archive and verified line by line. 249 Parks lines reconcile to $6,261.48 ex-GST to the cent (GL + support rollup); WINC ABN 94 000 728 398 PASS on all nine; per-line GST $506.56 on $5,065.69 taxable, 34 lines $1,195.79 GST-free food (no ITC). L3 Evidence and L4 Tax AMBER-&gt;GREEN. L2 NA stays RED (recode held on Finance acceptance), overall AMBER on Finance items only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Confirm Finance accepts WINC systemic recode out of 73563. 2 Confirm TE005250 desk risers 72313 vs 72111. 3 Confirm 73512 movements Reason B (filter 50/50). 4 Release CN-23167. + Sight the 9 unsighted WINC source invoices (9901690129, 9901699602, 9901709054, 9901718415, 9901727996, 9901737473, 9901746332, 9901754676, 9901773647) for line-level support of the recode. UPDATE 9-Jun: nine WINC invoices SIGHTED and filed; evidence + tax limbs cleared. Remaining holds are Finance-side only (accept WINC recode; 72313 vs 72111 risers; Reason B/50-50 filter).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA73563_Evidence/ (11 WINC invoices incl 9 newly sighted P1-P10, Officeworks 628185694, audit, recon, ledger)</t>
   </si>
   <si>
     <t xml:space="preserve">72114</t>
@@ -1012,7 +1012,7 @@
         <v>30</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>29</v>

--- a/00_Account_Review_Register.xlsx
+++ b/00_Account_Review_Register.xlsx
@@ -25,7 +25,7 @@
     <t xml:space="preserve">LCC Parks 4090000  —  Account Review Register</t>
   </si>
   <si>
-    <t xml:space="preserve">Four-limb verification: PK | Natural account | Evidence | Tax compliance.  RED blocker  AMBER confirm  GREEN clear.  Running journal batch CN-23167.  Updated 9-Jun-2026 (integrated 9-Jun-2026: 73563 recode sign-correction carried; 73564 tax and 73563 evidence reverted to AMBER per the evidence rule).  73533 cleared GREEN (9-Jun): 7-Eleven receipt sighted and $6.55 recoded to 73512; hotel GST substantiation waived by Spero.</t>
+    <t xml:space="preserve">Four-limb verification: PK | Natural account | Evidence | Tax compliance.  RED blocker  AMBER confirm  GREEN clear.  Running journal batch CN-23167.  Updated 9-Jun-2026 (integrated 9-Jun-2026: 73563 recode sign-correction carried; 73564 tax and 73563 evidence reverted to AMBER per the evidence rule).  73533 cleared GREEN (9-Jun): 7-Eleven receipt sighted and $6.55 recoded to 73512; hotel GST substantiation waived by Spero.  POLICY 9-Jun: no emails are sent (Finance included); decisions are Spero's and prepared recodes are journal-ready (no Finance-acceptance gate). Outstanding lines live in this register and the live journal 00_Live_Recode_Journal.xlsx.</t>
   </si>
   <si>
     <t xml:space="preserve">Account</t>
@@ -94,7 +94,7 @@
     <t xml:space="preserve">NA73564_Evidence/ (Esri INV000555 sighted; ledger extract); NA73564_GENJNL_Recode.txt (held)</t>
   </si>
   <si>
-    <t xml:space="preserve">CN-23167 (A 73564-&gt;73566 HELD-Finance; B 3 PK net-moves PREPARED per directive)</t>
+    <t xml:space="preserve">CN-23167 (journal-ready, Spero; A 73564-&gt;73566 software, B 3 PK net-moves)</t>
   </si>
   <si>
     <t xml:space="preserve">9-Jun-2026</t>
@@ -145,7 +145,7 @@
     <t xml:space="preserve">NA72312_Evidence/ (IKEA TE004431; Empire RL196475; ledger extract)</t>
   </si>
   <si>
-    <t xml:space="preserve">CN-23167 (held)</t>
+    <t xml:space="preserve">CN-23167 (journal-ready, Spero)</t>
   </si>
   <si>
     <t xml:space="preserve">8-Jun-2026</t>

--- a/00_Account_Review_Register.xlsx
+++ b/00_Account_Review_Register.xlsx
@@ -202,13 +202,13 @@
     <t xml:space="preserve">N/A</t>
   </si>
   <si>
-    <t xml:space="preserve">3-Jun Reali PK split $1,059.76 confirmed subset (~4%). GJ SOURCE NOW SIGHTED (Document Reconstruction, doc 202603161072172000000001, ledger 26SLACT): a BALANCED multi-account recode batch (nets $0.00). Its 72114 block credits $10,650.27 from 1-20001-72114 narrated 'Institute of Public Works Engineering Au' (IPWEA) and DEBITS the same $10,650.27 across 16 service-level 72114 (Uniforms) PKs. CONCERN: if the $10,650.27 is a genuine IPWEA professional charge it should leave 72114 entirely (73542 Professional Membership most likely, or 73541 Conferences / 73544 Training), not be redistributed WITHIN Uniforms. Wider Reali standing-order set ($17,288.98) now provided (C00223414 zip), not yet worked.</t>
+    <t xml:space="preserve">3-Jun Reali PK split $1,059.76 confirmed subset (~4%). GJ SOURCE NOW SIGHTED (Document Reconstruction, doc 202603161072172000000001, ledger 26SLACT): a BALANCED multi-account recode batch (nets $0.00). Its 72114 block credits $10,650.27 from 1-20001-72114 narrated 'Institute of Public Works Engineering Au' (IPWEA) and DEBITS the same $10,650.27 across 16 service-level 72114 (Uniforms) PKs. CONCERN: if the $10,650.27 is a genuine IPWEA professional charge it should leave 72114 entirely (73542 Professional Membership most likely, or 73541 Conferences / 73544 Training), not be redistributed WITHIN Uniforms. Wider Reali standing-order set ($17,288.98) now provided (C00223414 zip), not yet worked. LIVE LISTING 9-Jun: 00_Uniform_Listing_72114.xlsx built from fresh TechOne export - full account 103 lines $26,236.42, 22 service codes. L1 Svc/PK 98 GREEN / 5 AMBER (off-home/unmapped); 57 of 103 lines have NO attachment (RED evidence); 46 have attachments (pending sighting). IPWEA -$10,650.27 (GJ078546) flagged to 73542. Reviewed-$ in this register stays the $1,059.76 Reali subset; the listing is the live per-line state.</t>
   </si>
   <si>
     <t xml:space="preserve">1 Confirm whether the reconstruction batch is POSTED or PROPOSED; if posted, the IPWEA $10,650.27 is already spread across Uniforms service PKs. 2 Obtain the underlying IPWEA invoice to confirm nature (membership vs conference vs training) and set destination (73542/73541/73544); it should not sit in 72114. 3 Work the now-provided Reali set at full scope. 4 Confirm net-movement vs full-reversal format. Same batch also shows other apparent miscodes outside scope (e.g. Empire Office Furniture $4,300 in 73544 Training).</t>
   </si>
   <si>
-    <t xml:space="preserve">NA72114_Scope_Note.md; Document_Reconstruction (GJ source) sighted; C00223414 Reali set provided</t>
+    <t xml:space="preserve">NA72114_Scope_Note.md; Document_Reconstruction (GJ source) sighted; C00223414 Reali set provided; 00_Uniform_Listing_72114.xlsx (full account, per-line)</t>
   </si>
   <si>
     <t xml:space="preserve">73140</t>

--- a/00_Account_Review_Register.xlsx
+++ b/00_Account_Review_Register.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="182">
   <si>
     <t xml:space="preserve">LCC Parks 4090000  —  Account Review Register</t>
   </si>
@@ -445,7 +445,7 @@
     <t xml:space="preserve">Full account: 114 lines, 23 cost codes; section subsets verified (Natural Areas $116,963.24, Depots $23,626.58)</t>
   </si>
   <si>
-    <t xml:space="preserve">Reconciles to SE2 to the cent ($236,378.27, variance $0.00). Six findings: F1 $5,635 double-posted to PK000022 (GJ079190 duplicates GJ079210; phantom -$5,635 credit on 20392/PK000511; both narrated "Timber Treatment (PK000510)", describing neither); F2 ~$98,005 above-threshold contract spend, 73212 candidates (LCC31326 $25,848.08; Destination Trails series $43,114; Chronicle series $29,042.45); F3 training/equipment on a contracts account (PRINCE2 $2,440 to 73544; GJ078546 legs PSIA $4,300 + IPWEA $2,788 + chair $370.05 to 72313, destinations unverified); F4 GJ078546 $11,098.91 consultancy reversal destination unverified, plus Provac $2,050 grave-dig plant hire inbound query; F5 SC10918 -$154 plaque credit on Depots PK000001 (cemeteries item); F6 advisory $0.01 RL195364 variance line. No line carries sighted Tier 1 evidence (attachment flags are not sighting); no recode dollar populated, no GENJNL (un-instructed). 11-Jun-2026 intake C00228240: 43 evidence documents sighted and filed, $157,051.42 of $236,378.27 (66.4%) now evidenced, every document exact to its GL line on the x1.1 test; 18 ABN checksums PASS; INCON ABR sighted (active, GST registered, Edenstone name matches; young-entity NOTE). F5 (SC10918 scrap credit) and F6 ($0.01 = Empire GST rounding cent) CLOSED. F1 enriched: Gihani 6-May-2026 email instructs PK000510 to PK000023 and PK000511 to PK000022; both GJ079190/GJ079210 posted to PK000022, so GJ079190 is the 510 batch misposted or a duplicate - ruling now includes the correct re-post destination. NEW F7: TE004838 Message Media $242.40 posted 1-20241-73211 against a cover slip coding PK000055-73212. New classification candidates: Firesight $12,800 to 73601 (consultancy test reads met); Chronicle INV-0868 $5,812.45 software to 73566; Tennyson 27168 $1,058 signage to 72222; SC10918 scrap income to 64411; Telstra series $9,237.48 telecoms query; INCON $25,848.08 is materials supply not contract services.</t>
+    <t xml:space="preserve">Reconciles to SE2 to the cent ($236,378.27, variance $0.00). Six findings: F1 $5,635 double-posted to PK000022 (GJ079190 duplicates GJ079210; phantom -$5,635 credit on 20392/PK000511; both narrated "Timber Treatment (PK000510)", describing neither); F2 ~$98,005 above-threshold contract spend, 73212 candidates (LCC31326 $25,848.08; Destination Trails series $43,114; Chronicle series $29,042.45); F3 training/equipment on a contracts account (PRINCE2 $2,440 to 73544; GJ078546 legs PSIA $4,300 + IPWEA $2,788 + chair $370.05 to 72313, destinations unverified); F4 GJ078546 $11,098.91 consultancy reversal destination unverified, plus Provac $2,050 grave-dig plant hire inbound query; F5 SC10918 -$154 plaque credit on Depots PK000001 (cemeteries item); F6 advisory $0.01 RL195364 variance line. No line carries sighted Tier 1 evidence (attachment flags are not sighting); no recode dollar populated, no GENJNL (un-instructed). 11-Jun-2026 intake C00228240: 43 evidence documents sighted and filed, $157,051.42 of $236,378.27 (66.4%) now evidenced, every document exact to its GL line on the x1.1 test; 18 ABN checksums PASS; INCON ABR sighted (active, GST registered, Edenstone name matches; young-entity NOTE). F5 (SC10918 scrap credit) and F6 ($0.01 = Empire GST rounding cent) CLOSED. F1 enriched: Gihani 6-May-2026 email instructs PK000510 to PK000023 and PK000511 to PK000022; both GJ079190/GJ079210 posted to PK000022, so GJ079190 is the 510 batch misposted or a duplicate - ruling now includes the correct re-post destination. NEW F7: TE004838 Message Media $242.40 posted 1-20241-73211 against a cover slip coding PK000055-73212. New classification candidates: Firesight $12,800 to 73601 (consultancy test reads met); Chronicle INV-0868 $5,812.45 software to 73566; Tennyson 27168 $1,058 signage to 72222; SC10918 scrap income to 64411; Telstra series $9,237.48 telecoms query; INCON $25,848.08 is materials supply not contract services. RE-EXPORT 16-Jun-2026 (ledger dated 17-Jun): account refreshed from 114 lines $236,378.27 to 120 lines $267,532.19. The prior 114 lines are unchanged; 6 new P12 lines add $31,153.92 (INV-0356 Destination Trails $24,340.00 plus five standing-order lines: 00031242 $3,665, INV-1407 $1,541.82, 00031269 $1,083, 00001168 $400, 00061080 $124.10). The 6 new lines and ~30 supporting documents received this session (AP coversheets, Document Reconstructions, FBT/GST correction working, P6 accruals, two journal .msg emails) are archived raw in _Sources_16-Jun-2026/NA73211_ReExport_17-Jun/ and NOT yet worked; the 6 lines sit PENDING in the listing, evidence and tax limbs unmoved.</t>
   </si>
   <si>
     <t xml:space="preserve">1 Spero instruction on F1 GJ079190 (reversal, and whether the 510 batch re-posts to PK000023 per the Gihani email). 2 Spero rulings on the candidate set: F2 contract-floor recodes; F3 training/chair destinations (PSIA, IPWEA, DDLS, Empire now evidenced); Firesight 73601; Chronicle 73566/survey; Tennyson 72222; SC10918 64411 + cemeteries attribution; TE004838 (F7); Telstra telecoms; INCON materials. 3 Obtain the residual gap list (manifest GAP rows): 2906937 $10,200; 2908705 $17,000; TBM x4 $15,604.11; Ausecology INV-4029/4030 $14,840; Provac INV-00037183 $2,050; Telstra Dec-25 $727.95; T2 3222869/3223786 $1,820; 698933AU/713170AU $2,433.44; EWN INV-14768; 9016 $1,710; 00735 $200; 34828 $546.68; INV-38877 $2,250; 00059013/00031xxx/00060xxx series $2,438.20. 4 ABR sightings queue (17 suppliers). 5 IPWEA $343.20 part-payment posting trace ($312.00 ex + $31.20 GST).</t>
@@ -457,7 +457,7 @@
     <t xml:space="preserve">n/a (no recode staged; findings held un-instructed)</t>
   </si>
   <si>
-    <t xml:space="preserve">11-Jun-2026 (intake C00228240 applied)</t>
+    <t xml:space="preserve">16-Jun-2026 (re-export 17-Jun: +6 P12 lines, +$31,153.92)</t>
   </si>
   <si>
     <t xml:space="preserve">62121/62125</t>
@@ -539,6 +539,30 @@
   </si>
   <si>
     <t xml:space="preserve">n/a (TE004218 recode already in-ledger via GJ078933)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7B213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal - Medical Services (Immunisation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whole-branch immunisation on NatAreas PK000432 (svc 20318); 70 lines P2-P12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal immunisation recharge, $4,861.70 ex-GST over 70 lines P2-P12, miscoded at PK level: Internal_Medical.XLSM 'Lookup Values' row 23 maps the whole 4090000 Parks branch to one ledger line PK000432-7B213 (svc 20318 Natural Areas), so every Parks employee's immunisation charge lands on Natural Areas regardless of section. Natural account 7B213 and the per-line amounts are not in dispute (L2 GREEN); the defect is Limb 1 PK attribution. Staged svc-PK split reallocates $3,799.50 over 17 pairs to home PKs (Park Maintenance PK000003/PK000012, Rangers PK000084, Trees PK000433, Park Services PK000435, NatAreas PK000431), nets $0.00, source PK000432 signed sum -$3,799.50, every pair passes pk_validator and the 40-char cap. Stays on PK000432: $541.30 (James Lloyd-Jones $338.30, Renee Hoyle $82.00 correct; Arno Schneider $121.00 held pending section). Off-branch (not Parks) $520.90 incl a $146.30 duplicate, cross-branch, needs Finance. Sonya Karlsson/Christian De Leon/Gregory Cavell are Spero-instructed placements (not on the roster). Internal account: no GST event, L4 n/a. SE2 reconciliation not yet performed; no account-level GREEN until it ties.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Supply Arno Schneider's section to add his pair to the recode. 2 Confirm whether Park Maintenance staff resolve to PK000012 vs PK000003 by substantive position. 3 Hand the off-branch SL reversal draft and the $146.30 duplicate query to Finance. 4 Fix Internal_Medical.XLSM row 23 to a per-section Parks lookup so the miscode stops recurring. 5 Sight the immunisation IJ backings (evidence GAP, all 70 lines unsighted). 6 Tie the export to SE2 to the cent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA7B213_Verification_Record.md; NA7B213_GENJNL_Recode.txt; NA7B213_Employee_PK_Mapping.csv; NA7B213_Held_Items.md; NA7B213_Evidence/ (GAP, unsighted)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN-23167 (journal-ready, Spero; $3,799.50 svc-PK split, 17 pairs, nets $0.00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16-Jun-2026</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL reviewed $ (this register)</t>
@@ -705,56 +729,60 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1010,7 +1038,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
@@ -1580,7 +1608,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>93</v>
       </c>
@@ -1627,7 +1655,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
         <v>99</v>
       </c>
@@ -1674,7 +1702,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>107</v>
       </c>
@@ -1721,7 +1749,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
         <v>114</v>
       </c>
@@ -1768,7 +1796,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
         <v>121</v>
       </c>
@@ -1815,7 +1843,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
         <v>128</v>
       </c>
@@ -1862,7 +1890,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="294" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="294" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
         <v>138</v>
       </c>
@@ -1873,10 +1901,10 @@
         <v>140</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>236378.27</v>
+        <v>267532.19</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>260016.1</v>
+        <v>294285.41</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>20</v>
@@ -1909,7 +1937,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
         <v>146</v>
       </c>
@@ -1956,7 +1984,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
         <v>153</v>
       </c>
@@ -2003,7 +2031,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
         <v>160</v>
       </c>
@@ -2050,7 +2078,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
         <v>166</v>
       </c>
@@ -2097,17 +2125,64 @@
         <v>106</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="11" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="D26" s="12" t="n">
-        <f aca="false">SUM(D5:D25)</f>
-        <v>502932.11</v>
-      </c>
-      <c r="E26" s="12" t="n">
-        <f aca="false">SUM(E5:E25)</f>
-        <v>551833.64</v>
+      <c r="B26" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>4861.7</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>4861.7</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="N26" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C27" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <f aca="false">SUM(D5:D26)</f>
+        <v>538947.73</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <f aca="false">SUM(E5:E26)</f>
+        <v>590964.65</v>
       </c>
     </row>
   </sheetData>

--- a/00_Account_Review_Register.xlsx
+++ b/00_Account_Review_Register.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="183">
   <si>
     <t xml:space="preserve">LCC Parks 4090000  —  Account Review Register</t>
   </si>
@@ -394,18 +394,21 @@
     <t xml:space="preserve">Full account: PK000087 svc20001 (single engagement, Org Risk Consulting)</t>
   </si>
   <si>
-    <t xml:space="preserve">Full account parsed, 9 lines $46,003.66, reconciles to SE2 exact. Single engagement: Organisational Risk Consulting Pty Ltd, Parks Branch WHS Gap Analysis (Consultancy Agreement, T&amp;M, consultant Andrea Paynter, PO 711200/712924). 1 of 9 invoices sighted: INV-251010(2) $2,132.63 via GJ078546, GST $213.26 exact, $2,345.89 incl = GL x 1.1 exact; consultancy four-element test met on the face; 73601 correct. Invoice addressee corroborates Anita Moore as Acting Parks Manager (bears on her home-service confirmation). 8 invoices $43,871.03 UNSIGHTED (INV-250714, 250811-13, 250910-13): evidence and tax limbs AMBER per the evidence rule. Budget $45,000; $1,003.66 (2.2%) over.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Obtain the 8 Org Risk invoices ($43,871.03). 2 Run ABR/ASIC dossier on ABN 27 651 588 662 when the set lands. 3 Check engagement period vs the 12-month contractor cap (runs 30-Jul-2025 onward on sighted docs).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA73601_Evidence/ (INV-251010(2) + ledger extract); NA73601_Evidence_Manifest.csv (gap-listed)</t>
+    <t xml:space="preserve">Full account parsed, 9 lines $46,003.66, reconciles to SE2 exact. Single engagement: Organisational Risk Consulting Pty Ltd, Parks Branch WHS Gap Analysis (Consultancy Agreement, T&amp;M, consultant Andrea Paynter, PO 711200/712924). 1 of 9 invoices sighted: INV-251010(2) $2,132.63 via GJ078546, GST $213.26 exact, $2,345.89 incl = GL x 1.1 exact; consultancy four-element test met on the face; 73601 correct. Invoice addressee corroborates Anita Moore as Acting Parks Manager (bears on her home-service confirmation). 8 invoices $43,871.03 UNSIGHTED (INV-250714, 250811-13, 250910-13): evidence and tax limbs AMBER per the evidence rule. Budget $45,000; $1,003.66 (2.2%) over. EVIDENCE CLOSED 16-Jun-2026: the eight outstanding Organisational Risk Consulting weekly invoices (INV-250714/250811/250812/250813/250910/250911/250912/250913) are sighted in the 17-Jun intake, summing to $43,871.03 exact against the GAP; ABN 27 651 588 662 checksum PASS, GST disclosed = ex x 0.1 and incl = ex x 1.1 on every invoice. With L03 already sighted the account is 9 of 9 invoices, $46,003.66 reconciled to the cent. L3 Evidence and L4 Tax move to GREEN; account is now GREEN.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account fully evidenced and reconciled; no open actions. (Prior 8-invoice GAP closed 16-Jun-2026.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA73601_Evidence/ (9 of 9 invoices sighted; ledger extract); NA73601_Evidence_Manifest.csv</t>
   </si>
   <si>
     <t xml:space="preserve">n/a (no recode expected; coding correct on sighted line)</t>
   </si>
   <si>
+    <t xml:space="preserve">16-Jun-2026 (8 invoices sighted; account GREEN)</t>
+  </si>
+  <si>
     <t xml:space="preserve">73123</t>
   </si>
   <si>
@@ -445,7 +448,7 @@
     <t xml:space="preserve">Full account: 114 lines, 23 cost codes; section subsets verified (Natural Areas $116,963.24, Depots $23,626.58)</t>
   </si>
   <si>
-    <t xml:space="preserve">Reconciles to SE2 to the cent ($236,378.27, variance $0.00). Six findings: F1 $5,635 double-posted to PK000022 (GJ079190 duplicates GJ079210; phantom -$5,635 credit on 20392/PK000511; both narrated "Timber Treatment (PK000510)", describing neither); F2 ~$98,005 above-threshold contract spend, 73212 candidates (LCC31326 $25,848.08; Destination Trails series $43,114; Chronicle series $29,042.45); F3 training/equipment on a contracts account (PRINCE2 $2,440 to 73544; GJ078546 legs PSIA $4,300 + IPWEA $2,788 + chair $370.05 to 72313, destinations unverified); F4 GJ078546 $11,098.91 consultancy reversal destination unverified, plus Provac $2,050 grave-dig plant hire inbound query; F5 SC10918 -$154 plaque credit on Depots PK000001 (cemeteries item); F6 advisory $0.01 RL195364 variance line. No line carries sighted Tier 1 evidence (attachment flags are not sighting); no recode dollar populated, no GENJNL (un-instructed). 11-Jun-2026 intake C00228240: 43 evidence documents sighted and filed, $157,051.42 of $236,378.27 (66.4%) now evidenced, every document exact to its GL line on the x1.1 test; 18 ABN checksums PASS; INCON ABR sighted (active, GST registered, Edenstone name matches; young-entity NOTE). F5 (SC10918 scrap credit) and F6 ($0.01 = Empire GST rounding cent) CLOSED. F1 enriched: Gihani 6-May-2026 email instructs PK000510 to PK000023 and PK000511 to PK000022; both GJ079190/GJ079210 posted to PK000022, so GJ079190 is the 510 batch misposted or a duplicate - ruling now includes the correct re-post destination. NEW F7: TE004838 Message Media $242.40 posted 1-20241-73211 against a cover slip coding PK000055-73212. New classification candidates: Firesight $12,800 to 73601 (consultancy test reads met); Chronicle INV-0868 $5,812.45 software to 73566; Tennyson 27168 $1,058 signage to 72222; SC10918 scrap income to 64411; Telstra series $9,237.48 telecoms query; INCON $25,848.08 is materials supply not contract services. RE-EXPORT 16-Jun-2026 (ledger dated 17-Jun): account refreshed from 114 lines $236,378.27 to 120 lines $267,532.19. The prior 114 lines are unchanged; 6 new P12 lines add $31,153.92 (INV-0356 Destination Trails $24,340.00 plus five standing-order lines: 00031242 $3,665, INV-1407 $1,541.82, 00031269 $1,083, 00001168 $400, 00061080 $124.10). The 6 new lines and ~30 supporting documents received this session (AP coversheets, Document Reconstructions, FBT/GST correction working, P6 accruals, two journal .msg emails) are archived raw in _Sources_16-Jun-2026/NA73211_ReExport_17-Jun/ and NOT yet worked; the 6 lines sit PENDING in the listing, evidence and tax limbs unmoved.</t>
+    <t xml:space="preserve">Reconciles to SE2 to the cent ($236,378.27, variance $0.00). Six findings: F1 $5,635 double-posted to PK000022 (GJ079190 duplicates GJ079210; phantom -$5,635 credit on 20392/PK000511; both narrated "Timber Treatment (PK000510)", describing neither); F2 ~$98,005 above-threshold contract spend, 73212 candidates (LCC31326 $25,848.08; Destination Trails series $43,114; Chronicle series $29,042.45); F3 training/equipment on a contracts account (PRINCE2 $2,440 to 73544; GJ078546 legs PSIA $4,300 + IPWEA $2,788 + chair $370.05 to 72313, destinations unverified); F4 GJ078546 $11,098.91 consultancy reversal destination unverified, plus Provac $2,050 grave-dig plant hire inbound query; F5 SC10918 -$154 plaque credit on Depots PK000001 (cemeteries item); F6 advisory $0.01 RL195364 variance line. No line carries sighted Tier 1 evidence (attachment flags are not sighting); no recode dollar populated, no GENJNL (un-instructed). 11-Jun-2026 intake C00228240: 43 evidence documents sighted and filed, $157,051.42 of $236,378.27 (66.4%) now evidenced, every document exact to its GL line on the x1.1 test; 18 ABN checksums PASS; INCON ABR sighted (active, GST registered, Edenstone name matches; young-entity NOTE). F5 (SC10918 scrap credit) and F6 ($0.01 = Empire GST rounding cent) CLOSED. F1 enriched: Gihani 6-May-2026 email instructs PK000510 to PK000023 and PK000511 to PK000022; both GJ079190/GJ079210 posted to PK000022, so GJ079190 is the 510 batch misposted or a duplicate - ruling now includes the correct re-post destination. NEW F7: TE004838 Message Media $242.40 posted 1-20241-73211 against a cover slip coding PK000055-73212. New classification candidates: Firesight $12,800 to 73601 (consultancy test reads met); Chronicle INV-0868 $5,812.45 software to 73566; Tennyson 27168 $1,058 signage to 72222; SC10918 scrap income to 64411; Telstra series $9,237.48 telecoms query; INCON $25,848.08 is materials supply not contract services. RE-EXPORT 16-Jun-2026 (ledger dated 17-Jun): account refreshed from 114 lines $236,378.27 to 120 lines $267,532.19. The prior 114 lines are unchanged; 6 new P12 lines add $31,153.92 (INV-0356 Destination Trails $24,340.00 plus five standing-order lines: 00031242 $3,665, INV-1407 $1,541.82, 00031269 $1,083, 00001168 $400, 00061080 $124.10). The 6 new lines and ~30 supporting documents received this session (AP coversheets, Document Reconstructions, FBT/GST correction working, P6 accruals, two journal .msg emails) are archived raw in _Sources_16-Jun-2026/NA73211_ReExport_17-Jun/ and NOT yet worked; the 6 lines sit PENDING in the listing, evidence and tax limbs unmoved. EVIDENCE 16-Jun-2026: 16 of the outstanding invoices are sighted from the 17-Jun intake (Lothian 2906937 $10,200 and 2908705 $17,000; TrailBuilders TBM 00097461/583/626/780; Ausecology INV-4029 $8,480 and INV-4030 $6,360; T2 Electrical 3222869/3223786; IDM 698933AU/713170AU; Radio Logan 9016; Treescape 34828; T&amp;H Levai INV-38877; Wildlife Qld 00735), +$66,404.23, all ABNs checksum PASS and GST exact. Six GAPs remain (Provac INV-00037183 $2,050, Telstra Dec-25 $727.95, EWN INV-14768, standing orders 00059013/00031055.../00060617...) plus the 6 new P12 lines unworked; Blackout catering inv 5468 received, an NA-classification candidate (73511/73512), held. L3 Evidence stays AMBER on the residue.</t>
   </si>
   <si>
     <t xml:space="preserve">1 Spero instruction on F1 GJ079190 (reversal, and whether the 510 batch re-posts to PK000023 per the Gihani email). 2 Spero rulings on the candidate set: F2 contract-floor recodes; F3 training/chair destinations (PSIA, IPWEA, DDLS, Empire now evidenced); Firesight 73601; Chronicle 73566/survey; Tennyson 72222; SC10918 64411 + cemeteries attribution; TE004838 (F7); Telstra telecoms; INCON materials. 3 Obtain the residual gap list (manifest GAP rows): 2906937 $10,200; 2908705 $17,000; TBM x4 $15,604.11; Ausecology INV-4029/4030 $14,840; Provac INV-00037183 $2,050; Telstra Dec-25 $727.95; T2 3222869/3223786 $1,820; 698933AU/713170AU $2,433.44; EWN INV-14768; 9016 $1,710; 00735 $200; 34828 $546.68; INV-38877 $2,250; 00059013/00031xxx/00060xxx series $2,438.20. 4 ABR sightings queue (17 suppliers). 5 IPWEA $343.20 part-payment posting trace ($312.00 ex + $31.20 GST).</t>
@@ -734,55 +737,55 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1818,14 +1821,14 @@
       <c r="G19" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H19" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>20</v>
+      <c r="H19" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="K19" s="5" t="s">
         <v>124</v>
@@ -1840,18 +1843,18 @@
         <v>127</v>
       </c>
       <c r="O19" s="5" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>0</v>
@@ -1860,45 +1863,45 @@
         <v>0</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="O20" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="294" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>267532.19</v>
@@ -1922,30 +1925,30 @@
         <v>20</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O21" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D22" s="6" t="n">
         <v>3711.73</v>
@@ -1969,16 +1972,16 @@
         <v>20</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O22" s="5" t="s">
         <v>106</v>
@@ -1986,13 +1989,13 @@
     </row>
     <row r="23" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>2944</v>
@@ -2010,22 +2013,22 @@
         <v>20</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>20</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O23" s="5" t="s">
         <v>106</v>
@@ -2033,13 +2036,13 @@
     </row>
     <row r="24" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D24" s="6" t="n">
         <v>7570.5</v>
@@ -2057,19 +2060,19 @@
         <v>20</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>20</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N24" s="5" t="s">
         <v>77</v>
@@ -2080,13 +2083,13 @@
     </row>
     <row r="25" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>642.14</v>
@@ -2110,16 +2113,16 @@
         <v>20</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N25" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O25" s="5" t="s">
         <v>106</v>
@@ -2127,13 +2130,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>4861.7</v>
@@ -2151,30 +2154,30 @@
         <v>20</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J26" s="9" t="s">
         <v>20</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N26" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O26" s="5" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C27" s="12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D27" s="13" t="n">
         <f aca="false">SUM(D5:D26)</f>

--- a/00_Account_Review_Register.xlsx
+++ b/00_Account_Review_Register.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="191">
   <si>
     <t xml:space="preserve">LCC Parks 4090000  —  Account Review Register</t>
   </si>
@@ -328,63 +328,66 @@
     <t xml:space="preserve">Full account: 41 lines, $69,232.16; 17 vendor docs + back-charges intake sighted</t>
   </si>
   <si>
-    <t xml:space="preserve">Account reconciles. 21 references evidenced incl Whitehead $18,750, Fire Mgmt $10,500, Bendelta $8,966.28 (consultancy recode candidate to 73601), BAL $1,767 (73541 candidate; HLW dossier sighted, tax invoice outstanding), PSIA narration error. GST errors: Blue Dog $11.73 (GSTE-25), Barter $9.52 (GSTE-26), OIR $8.76 corrected (GSTE-27). 11-Jun: PK-split recode STAGED $2,131.46 (GJ079650 chargebacks $949.64 + ACCA split $1,181.82, 9 lines, nets $0.00, re-verified); Pryor/Hambly held; Preussner GJ078933 reopened as a destination query (73545 vs 7B411 on the $931.20 leg). | 11-Jun: GJ076597 backup + L&amp;D email SIGHTED (non-attendance recharge batch, nets $0.00; Pryor $214.00 and Hambly $294.42 evidenced as L&amp;D non-attendance, home-PK ruling remains). OIR source receipt SIGHTED: licensee Renee Hoyle, $96.35, PK000383 ParkCare; Hood audit email corroborates GSTE-27.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Upload NA73544_GENJNL_Recode.txt (in the live journal). 2 Spero rulings: Bendelta-&gt;73601 $8,966.28; BAL 73541-vs-73544 $1,767; Warnholtz concurrence; Pryor PK000044-vs-PK000003 $214.00; Hambly $294.42 (not in map); Preussner destination query. 3 Sight: HLW tax invoice, OIR source receipt, 7 journal backups ~$11,100. 4 Confirm Moore/Moir/Funk services (EOM report). 5 BAS: GSTE-25/26 reversals. | 11-Jun: journal backups now 6 outstanding (~$10,600: IJ074222, GJ078710, GJ078895, GJ077155, GJ079267, GJ078296); OIR source receipt CLOSED.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA73544_Evidence/ (36 files: session set hash-verified + back-charges set hashed this session)</t>
+    <t xml:space="preserve">Account reconciles. 21 references evidenced incl Whitehead $18,750, Fire Mgmt $10,500, Bendelta $8,966.28 (consultancy recode candidate to 73601), BAL $1,767 (73541 candidate; HLW dossier sighted, tax invoice outstanding), PSIA narration error. GST errors: Blue Dog $11.73 (GSTE-25), Barter $9.52 (GSTE-26), OIR $8.76 corrected (GSTE-27). 11-Jun: PK-split recode STAGED $2,131.46 (GJ079650 chargebacks $949.64 + ACCA split $1,181.82, 9 lines, nets $0.00, re-verified); Pryor/Hambly held; Preussner GJ078933 reopened as a destination query (73545 vs 7B411 on the $931.20 leg). | 11-Jun: GJ076597 backup + L&amp;D email SIGHTED (non-attendance recharge batch, nets $0.00; Pryor $214.00 and Hambly $294.42 evidenced as L&amp;D non-attendance, home-PK ruling remains). OIR source receipt SIGHTED: licensee Renee Hoyle, $96.35, PK000383 ParkCare; Hood audit email corroborates GSTE-27. | 17-Jun: SIX journal backups SIGHTED (L23-L28), each a balanced Document Reconstruction netting $0.00 (IJ074222, GJ078710, GJ078895, GJ077155, GJ079267, GJ078296); journal-backup gap CLOSED. ACCA INV-11404 deficiency was stale: invoice held at L10 since 10-Jun (SHA 6126cdf2); EVID overlay lines 159-161 relinked to EVID-0148 from a stale placeholder (matcher miss corrected). Internal journals post cross-ledger to 26PSLACT/26RMACT/WW03; NA 73544 consistent throughout.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Upload NA73544_GENJNL_Recode.txt (in the live journal). 2 Spero rulings: Bendelta-&gt;73601 $8,966.28; BAL 73541-vs-73544 $1,767; Warnholtz concurrence; Pryor PK000044-vs-PK000003 $214.00; Hambly $294.42 (not in map); Preussner destination query. 3 Sight: HLW tax invoice, OIR source receipt, 7 journal backups ~$11,100. 4 Confirm Moore/Moir/Funk services (EOM report). 5 BAS: GSTE-25/26 reversals. | 11-Jun: journal backups now 6 outstanding (~$10,600: IJ074222, GJ078710, GJ078895, GJ077155, GJ079267, GJ078296); OIR source receipt CLOSED. | 17-Jun: item 3 journal backups (6) CLOSED at L23-L28; ACCA deficiency closed (relinked, was stale). Residual on item 3: HLW (BAL) compliant tax invoice still outstanding (tax limb AMBER). Items 1,2,4,5 unchanged (Bendelta/BAL/Pryor/Hambly/Preussner rulings still with Spero; BAL workshop receipt $1,943.70 in intake does NOT match $1,767 TE004334 - reconcile before it closes the 73541 candidate).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA73544_Evidence/ (46 files: 17-Jun added L23-L28 journal backups, SHA-verified)</t>
   </si>
   <si>
     <t xml:space="preserve">CN-23167 (journal-ready, Spero 11-Jun-2026; NA73544 PK-split stream in the live journal)</t>
   </si>
   <si>
+    <t xml:space="preserve">17-Jun-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Major Contracts (3 section exports)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water Parks svc20802 $900 + Design&amp;Capital svc20191 $15,100 + s4090230 $38,242.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1 Strategy $15,100 (PO 708258) fails 73212 twice: four-element consultancy test met AND PO sits under the $20,000 floor; recode candidate to 73601 held (Tier 1 complete: 3 invoices + ABR x2 + ASIC, GST exact, hours recompute). Aust Care $630 invoice names PK000496, ledger charged PK000469 (PK recode candidate). GJ079210 -$66,183.82 one-sided Play Force move is the open dollar; ~$30,000 standing-order lines vendor-blind. | 11-Jun: GJ079210 backup SIGHTED - balanced 6-line PK move PK000035 to PK000022 (73123 $79,418 / 73212 $66,183.82 / 73211 $5,635), nets $0.00, direction correct; the $66,184 open dollar CLOSES as explained (narration crossover advisory; PK000510/511 not in maps). GJ076924 backup SIGHTED - 95-line balanced redistribution, $1,914 leg explained.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Spero rulings: A1 $15,100 73212-&gt;73601 (73603 alt); Aust Care PK000469-&gt;PK000496 $630. 2 GJ079210 + GJ076924 backups CLOSED 11-Jun-2026 (sighted, balanced, direction verified). 3 Vendor invoices for s4090230 standing orders (~$30,000). 4 Contracts vs the $20k floor: LCC-09-2022, Aust Care SO, Play Force. 5 Trace IPWEA $343.20 part-payment. 6 Confirm Anita Moore home service (OrgRisk invoice now corroborates Acting Parks Manager).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA73212_Evidence/ (8 files, hash-verified)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a (candidates held, no recode staged)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Major Contracts - Partnership (Alliance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full account: PK000366 svc20511 (3 invoices) + 2 zero split lines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$4,739.00 of $4,739.00 (100%) miscoded into 73215, a RESTRICTED Alliance account (CEO approval required); none of the spend is Alliance partnership work. All 3 invoices SIGHTED 11-Jun-2026 and reconcile to the cent: TEC 3043 $2,340.00 (mow/brushcut Bromley St Cornubia, PAR/336K/2024), Austspray 155797 $900.00 (fenceline clean-up Yarrabilba), Austspray 157909 $1,499.00 (Frankland Ave infill planting). All on PK000366 General Landscape Improvement Fund, matching invoice PK refs. ABNs checksum PASS, ABR active + GST registered (TEC 11 600 627 343; Austspray 89 122 731 775); GST exact on all three. SE2 reconciles exact ($4,739.00). Recode candidate 73215 to 73126 Landscapers &amp; Gardeners, full-reversal, 3 pairs, nets $0.00; destination validates (pk_validator OK PK000366/20511/73126); source leg trips the 73215 restriction flag by design.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Spero ruling on the 73215 to 73126 recode $4,739.00 (candidate held, un-instructed; restriction handling on the source leg to confirm). 2 Advisory: vendor masked by STANDING ORDER 24/25 narrations; invoices supply Tier 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA73215_Evidence/ (3 invoices + ledger extract, SHA-256 in NA73215_Evidence_Manifest.csv)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a (candidate held, no recode staged)</t>
+  </si>
+  <si>
     <t xml:space="preserve">11-Jun-2026</t>
   </si>
   <si>
-    <t xml:space="preserve">73212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Major Contracts (3 section exports)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water Parks svc20802 $900 + Design&amp;Capital svc20191 $15,100 + s4090230 $38,242.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A1 Strategy $15,100 (PO 708258) fails 73212 twice: four-element consultancy test met AND PO sits under the $20,000 floor; recode candidate to 73601 held (Tier 1 complete: 3 invoices + ABR x2 + ASIC, GST exact, hours recompute). Aust Care $630 invoice names PK000496, ledger charged PK000469 (PK recode candidate). GJ079210 -$66,183.82 one-sided Play Force move is the open dollar; ~$30,000 standing-order lines vendor-blind. | 11-Jun: GJ079210 backup SIGHTED - balanced 6-line PK move PK000035 to PK000022 (73123 $79,418 / 73212 $66,183.82 / 73211 $5,635), nets $0.00, direction correct; the $66,184 open dollar CLOSES as explained (narration crossover advisory; PK000510/511 not in maps). GJ076924 backup SIGHTED - 95-line balanced redistribution, $1,914 leg explained.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Spero rulings: A1 $15,100 73212-&gt;73601 (73603 alt); Aust Care PK000469-&gt;PK000496 $630. 2 GJ079210 + GJ076924 backups CLOSED 11-Jun-2026 (sighted, balanced, direction verified). 3 Vendor invoices for s4090230 standing orders (~$30,000). 4 Contracts vs the $20k floor: LCC-09-2022, Aust Care SO, Play Force. 5 Trace IPWEA $343.20 part-payment. 6 Confirm Anita Moore home service (OrgRisk invoice now corroborates Acting Parks Manager).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA73212_Evidence/ (8 files, hash-verified)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n/a (candidates held, no recode staged)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Major Contracts - Partnership (Alliance)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full account: PK000366 svc20511 (3 invoices) + 2 zero split lines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$4,739.00 of $4,739.00 (100%) miscoded into 73215, a RESTRICTED Alliance account (CEO approval required); none of the spend is Alliance partnership work. All 3 invoices SIGHTED 11-Jun-2026 and reconcile to the cent: TEC 3043 $2,340.00 (mow/brushcut Bromley St Cornubia, PAR/336K/2024), Austspray 155797 $900.00 (fenceline clean-up Yarrabilba), Austspray 157909 $1,499.00 (Frankland Ave infill planting). All on PK000366 General Landscape Improvement Fund, matching invoice PK refs. ABNs checksum PASS, ABR active + GST registered (TEC 11 600 627 343; Austspray 89 122 731 775); GST exact on all three. SE2 reconciles exact ($4,739.00). Recode candidate 73215 to 73126 Landscapers &amp; Gardeners, full-reversal, 3 pairs, nets $0.00; destination validates (pk_validator OK PK000366/20511/73126); source leg trips the 73215 restriction flag by design.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Spero ruling on the 73215 to 73126 recode $4,739.00 (candidate held, un-instructed; restriction handling on the source leg to confirm). 2 Advisory: vendor masked by STANDING ORDER 24/25 narrations; invoices supply Tier 1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA73215_Evidence/ (3 invoices + ledger extract, SHA-256 in NA73215_Evidence_Manifest.csv)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n/a (candidate held, no recode staged)</t>
-  </si>
-  <si>
     <t xml:space="preserve">73601</t>
   </si>
   <si>
@@ -394,19 +397,19 @@
     <t xml:space="preserve">Full account: PK000087 svc20001 (single engagement, Org Risk Consulting)</t>
   </si>
   <si>
-    <t xml:space="preserve">Full account parsed, 9 lines $46,003.66, reconciles to SE2 exact. Single engagement: Organisational Risk Consulting Pty Ltd, Parks Branch WHS Gap Analysis (Consultancy Agreement, T&amp;M, consultant Andrea Paynter, PO 711200/712924). 1 of 9 invoices sighted: INV-251010(2) $2,132.63 via GJ078546, GST $213.26 exact, $2,345.89 incl = GL x 1.1 exact; consultancy four-element test met on the face; 73601 correct. Invoice addressee corroborates Anita Moore as Acting Parks Manager (bears on her home-service confirmation). 8 invoices $43,871.03 UNSIGHTED (INV-250714, 250811-13, 250910-13): evidence and tax limbs AMBER per the evidence rule. Budget $45,000; $1,003.66 (2.2%) over. EVIDENCE CLOSED 16-Jun-2026: the eight outstanding Organisational Risk Consulting weekly invoices (INV-250714/250811/250812/250813/250910/250911/250912/250913) are sighted in the 17-Jun intake, summing to $43,871.03 exact against the GAP; ABN 27 651 588 662 checksum PASS, GST disclosed = ex x 0.1 and incl = ex x 1.1 on every invoice. With L03 already sighted the account is 9 of 9 invoices, $46,003.66 reconciled to the cent. L3 Evidence and L4 Tax move to GREEN; account is now GREEN.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account fully evidenced and reconciled; no open actions. (Prior 8-invoice GAP closed 16-Jun-2026.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA73601_Evidence/ (9 of 9 invoices sighted; ledger extract); NA73601_Evidence_Manifest.csv</t>
+    <t xml:space="preserve">Full account parsed, 9 lines $46,003.66, reconciles to SE2 exact. Single engagement: Organisational Risk Consulting Pty Ltd, Parks Branch WHS Gap Analysis (Consultancy Agreement, T&amp;M, consultant Andrea Paynter, PO 711200/712924). 1 of 9 invoices sighted: INV-251010(2) $2,132.63 via GJ078546, GST $213.26 exact, $2,345.89 incl = GL x 1.1 exact; consultancy four-element test met on the face; 73601 correct. Invoice addressee corroborates Anita Moore as Acting Parks Manager (bears on her home-service confirmation). 8 invoices $43,871.03 UNSIGHTED (INV-250714, 250811-13, 250910-13): evidence and tax limbs AMBER per the evidence rule. Budget $45,000; $1,003.66 (2.2%) over. | 17-Jun MERGE: 8 Org Risk Consulting invoices sighted ($43,871.03 exact), ABN 27 651 588 662 PASS, GST exact; account 9 of 9, GREEN (ported from PR-8 reconciliation).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Obtain the 8 Org Risk invoices ($43,871.03). 2 Run ABR/ASIC dossier on ABN 27 651 588 662 when the set lands. 3 Check engagement period vs the 12-month contractor cap (runs 30-Jul-2025 onward on sighted docs).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA73601_Evidence/ (INV-251010(2) + ledger extract); NA73601_Evidence_Manifest.csv (gap-listed)</t>
   </si>
   <si>
     <t xml:space="preserve">n/a (no recode expected; coding correct on sighted line)</t>
   </si>
   <si>
-    <t xml:space="preserve">16-Jun-2026 (8 invoices sighted; account GREEN)</t>
+    <t xml:space="preserve">17-Jun-2026 (8 invoices sighted; GREEN)</t>
   </si>
   <si>
     <t xml:space="preserve">73123</t>
@@ -448,19 +451,19 @@
     <t xml:space="preserve">Full account: 114 lines, 23 cost codes; section subsets verified (Natural Areas $116,963.24, Depots $23,626.58)</t>
   </si>
   <si>
-    <t xml:space="preserve">Reconciles to SE2 to the cent ($236,378.27, variance $0.00). Six findings: F1 $5,635 double-posted to PK000022 (GJ079190 duplicates GJ079210; phantom -$5,635 credit on 20392/PK000511; both narrated "Timber Treatment (PK000510)", describing neither); F2 ~$98,005 above-threshold contract spend, 73212 candidates (LCC31326 $25,848.08; Destination Trails series $43,114; Chronicle series $29,042.45); F3 training/equipment on a contracts account (PRINCE2 $2,440 to 73544; GJ078546 legs PSIA $4,300 + IPWEA $2,788 + chair $370.05 to 72313, destinations unverified); F4 GJ078546 $11,098.91 consultancy reversal destination unverified, plus Provac $2,050 grave-dig plant hire inbound query; F5 SC10918 -$154 plaque credit on Depots PK000001 (cemeteries item); F6 advisory $0.01 RL195364 variance line. No line carries sighted Tier 1 evidence (attachment flags are not sighting); no recode dollar populated, no GENJNL (un-instructed). 11-Jun-2026 intake C00228240: 43 evidence documents sighted and filed, $157,051.42 of $236,378.27 (66.4%) now evidenced, every document exact to its GL line on the x1.1 test; 18 ABN checksums PASS; INCON ABR sighted (active, GST registered, Edenstone name matches; young-entity NOTE). F5 (SC10918 scrap credit) and F6 ($0.01 = Empire GST rounding cent) CLOSED. F1 enriched: Gihani 6-May-2026 email instructs PK000510 to PK000023 and PK000511 to PK000022; both GJ079190/GJ079210 posted to PK000022, so GJ079190 is the 510 batch misposted or a duplicate - ruling now includes the correct re-post destination. NEW F7: TE004838 Message Media $242.40 posted 1-20241-73211 against a cover slip coding PK000055-73212. New classification candidates: Firesight $12,800 to 73601 (consultancy test reads met); Chronicle INV-0868 $5,812.45 software to 73566; Tennyson 27168 $1,058 signage to 72222; SC10918 scrap income to 64411; Telstra series $9,237.48 telecoms query; INCON $25,848.08 is materials supply not contract services. RE-EXPORT 16-Jun-2026 (ledger dated 17-Jun): account refreshed from 114 lines $236,378.27 to 120 lines $267,532.19. The prior 114 lines are unchanged; 6 new P12 lines add $31,153.92 (INV-0356 Destination Trails $24,340.00 plus five standing-order lines: 00031242 $3,665, INV-1407 $1,541.82, 00031269 $1,083, 00001168 $400, 00061080 $124.10). The 6 new lines and ~30 supporting documents received this session (AP coversheets, Document Reconstructions, FBT/GST correction working, P6 accruals, two journal .msg emails) are archived raw in _Sources_16-Jun-2026/NA73211_ReExport_17-Jun/ and NOT yet worked; the 6 lines sit PENDING in the listing, evidence and tax limbs unmoved. EVIDENCE 16-Jun-2026: 16 of the outstanding invoices are sighted from the 17-Jun intake (Lothian 2906937 $10,200 and 2908705 $17,000; TrailBuilders TBM 00097461/583/626/780; Ausecology INV-4029 $8,480 and INV-4030 $6,360; T2 Electrical 3222869/3223786; IDM 698933AU/713170AU; Radio Logan 9016; Treescape 34828; T&amp;H Levai INV-38877; Wildlife Qld 00735), +$66,404.23, all ABNs checksum PASS and GST exact. Six GAPs remain (Provac INV-00037183 $2,050, Telstra Dec-25 $727.95, EWN INV-14768, standing orders 00059013/00031055.../00060617...) plus the 6 new P12 lines unworked; Blackout catering inv 5468 received, an NA-classification candidate (73511/73512), held. L3 Evidence stays AMBER on the residue.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Spero instruction on F1 GJ079190 (reversal, and whether the 510 batch re-posts to PK000023 per the Gihani email). 2 Spero rulings on the candidate set: F2 contract-floor recodes; F3 training/chair destinations (PSIA, IPWEA, DDLS, Empire now evidenced); Firesight 73601; Chronicle 73566/survey; Tennyson 72222; SC10918 64411 + cemeteries attribution; TE004838 (F7); Telstra telecoms; INCON materials. 3 Obtain the residual gap list (manifest GAP rows): 2906937 $10,200; 2908705 $17,000; TBM x4 $15,604.11; Ausecology INV-4029/4030 $14,840; Provac INV-00037183 $2,050; Telstra Dec-25 $727.95; T2 3222869/3223786 $1,820; 698933AU/713170AU $2,433.44; EWN INV-14768; 9016 $1,710; 00735 $200; 34828 $546.68; INV-38877 $2,250; 00059013/00031xxx/00060xxx series $2,438.20. 4 ABR sightings queue (17 suppliers). 5 IPWEA $343.20 part-payment posting trace ($312.00 ex + $31.20 GST).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02_NA73211_Minor_Contracts/ (verification record + addendum; NA73211_Evidence/ 43 files, SHA-256 manifest with GAP rows; Related/ Gihani F1 email, DocRecon, T2 email, FBT 73511 source workbook)</t>
+    <t xml:space="preserve">Reconciles to SE2 to the cent at the established scope ($236,378.27). 17-Jun-2026 evidence pass: 14 source invoices sighted exact to GL on the x1.1 test (Lockwise 2906937/2908705, TBM 97461/583/626/780, T2 3222869/3223786, Easy Signs 698933AU/713170AU, T&amp;H Levai INV-38877, 9016, Australasia 34828, 00735), all 8 distinct vendor ABN checksums PASS, GST math clean (no GST errors). Ausecology INV-4029 $8,480 + INV-4030 $6,360 sighted but $450 residual in GJ078960 and vendor ABN not on invoice (NARROWED). Evidence sighted now $208,815.65 of $236,378.27 (88.3%), $223,655.65 (94.6%) incl Ausecology narrowed. | 17-Jun MERGE: refreshed to 120 lines $267,532.19 (+6 P12 lines from the 17-Jun re-export, +$31,153.92) and 16 outstanding invoices sighted (+$66,404.23; Lothian, TBM, Ausecology, T2 Electrical, IDM, Radio Logan, Treescape, T&amp;H Levai, Wildlife Qld) - ported from PR-8.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residual evidence GAP (~$5,505 quantified + EWN): small series 00059013/00031055/79/85/86/00060617/47 ($2,438.20), Provac INV-00037183 ($2,050), Telstra Dec-25 ($727.95), EWN INV-14768 (amount tbc); Ausecology $450 residual + vendor ABN. SCOPE: fresh 17-Jun export totals $267,532.19 vs register $236,378.27, delta $31,153.92 (suspected added P11/P12 lines incl 8 Org Risk Consulting WHS invoices INV-250714/811-813/910-913 present in intake but absent from 73211 ledger refs) - reconcile before changing scope. F1-F7 and candidate rulings still Spero's.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02_NA73211_Minor_Contracts/ (verification record + 11-Jun + 17-Jun addenda; NA73211_Evidence/ 59 files; NA73211_Evidence_Manifest.csv; NA73211_EvidencePass_17-Jun-2026.csv)</t>
   </si>
   <si>
     <t xml:space="preserve">n/a (no recode staged; findings held un-instructed)</t>
   </si>
   <si>
-    <t xml:space="preserve">16-Jun-2026 (re-export 17-Jun: +6 P12 lines, +$31,153.92)</t>
+    <t xml:space="preserve">17-Jun-2026 (re-export +6 lines; 16 invoices sighted)</t>
   </si>
   <si>
     <t xml:space="preserve">62121/62125</t>
@@ -542,6 +545,27 @@
   </si>
   <si>
     <t xml:space="preserve">n/a (TE004218 recode already in-ledger via GJ078933)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garbage Collection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PK000001 svc20151 + PK000022 svc20392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cleanaway allocated garbage slice; coding correct, reconciles to SE2 $0.00. F1 5 of 9 months unsighted; F2 no Parks tax invoice by design; F3 EOM accrual nets $0.00; F4 ABN not sighted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4: Cleanaway statements Jul/Sep/Dec 2025; 7 monthly allocation journals; sight &amp; validate Cleanaway ABN; Sep GJ077308 attachment flag N.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA73122_Evidence/ + 4 council-wide Cleanaway statements fingerprinted in manifest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIL recode (coding correct)</t>
   </si>
   <si>
     <t xml:space="preserve">7B213</t>
@@ -737,55 +761,55 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1041,7 +1065,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
@@ -1611,7 +1635,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="53.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
         <v>93</v>
       </c>
@@ -1658,7 +1682,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
         <v>99</v>
       </c>
@@ -1705,7 +1729,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>107</v>
       </c>
@@ -1752,7 +1776,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
         <v>114</v>
       </c>
@@ -1796,18 +1820,18 @@
         <v>120</v>
       </c>
       <c r="O18" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>46003.66</v>
@@ -1831,30 +1855,30 @@
         <v>29</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O19" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>0</v>
@@ -1863,45 +1887,45 @@
         <v>0</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O20" s="5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="294" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>267532.19</v>
@@ -1925,30 +1949,30 @@
         <v>20</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O21" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D22" s="6" t="n">
         <v>3711.73</v>
@@ -1972,30 +1996,30 @@
         <v>20</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>2944</v>
@@ -2013,36 +2037,36 @@
         <v>20</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>20</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="95.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D24" s="6" t="n">
         <v>7570.5</v>
@@ -2060,36 +2084,36 @@
         <v>20</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>20</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N24" s="5" t="s">
         <v>77</v>
       </c>
       <c r="O24" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="84.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>642.14</v>
@@ -2113,79 +2137,126 @@
         <v>20</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N25" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O25" s="5" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D26" s="6" t="n">
+        <v>21876.6</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>24064.26</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="N26" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="D27" s="6" t="n">
         <v>4861.7</v>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="E27" s="6" t="n">
         <v>4861.7</v>
       </c>
-      <c r="F26" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="M26" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="N26" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="O26" s="5" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C27" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="D27" s="13" t="n">
-        <f aca="false">SUM(D5:D26)</f>
-        <v>538947.73</v>
-      </c>
-      <c r="E27" s="13" t="n">
-        <f aca="false">SUM(E5:E26)</f>
-        <v>590964.65</v>
+      <c r="F27" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="N27" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="O27" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C28" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <f aca="false">SUM(D5:D27)</f>
+        <v>560824.33</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <f aca="false">SUM(E5:E27)</f>
+        <v>615028.91</v>
       </c>
     </row>
   </sheetData>

--- a/00_Account_Review_Register.xlsx
+++ b/00_Account_Review_Register.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="190">
   <si>
     <t xml:space="preserve">LCC Parks 4090000  —  Account Review Register</t>
   </si>
@@ -220,7 +220,7 @@
     <t xml:space="preserve">CV Check PK000001 svc20001</t>
   </si>
   <si>
-    <t xml:space="preserve">Carried from 3-Jun pass. 21 lines, single vendor (CV Check), narration consistent, NA matches chart definition; coding correct. $58.02 GJ EOY reversal normal. Tier-3 sighting only: AP invoices not sighted, so evidence and tax limbs remain open. 11-Jun-2026: five Kinatico Limited tax invoices received in intake (ABN 25 111 728 842, PO 801790, monthly pre-employment screening; Kinatico is the CVCheck parent): P00075671 Jul-2025, P00081314 Dec-2025, P00082255 Jan-2026, P00083290 Feb-2026, P00086890 May-2026. All five AP document numbers searched across every 11-Jun ledger export: zero hits. Held unapplied in 07_Intake_Held_Kinatico/ per the evidence rule; no limb moves until matched to 73140 ledger lines.</t>
+    <t xml:space="preserve">Carried from 3-Jun pass. 21 lines, single vendor (CV Check), narration consistent, NA matches chart definition; coding correct. $58.02 GJ EOY reversal normal. Tier-3 sighting only: AP invoices not sighted, so evidence and tax limbs remain open. 11-Jun-2026: five Kinatico Limited tax invoices received in intake (ABN 25 111 728 842, PO 801790, monthly pre-employment screening; Kinatico is the CVCheck parent): P00075671 Jul-2025, P00081314 Dec-2025, P00082255 Jan-2026, P00083290 Feb-2026, P00086890 May-2026. All five AP document numbers searched across every 11-Jun ledger export: zero hits. Held unapplied in 07_Intake_Held_Kinatico/ per the evidence rule; no limb moves until matched to 73140 ledger lines. | 17-Jun: five held Kinatico invoices VERIFIED (ABN 25 111 728 842 checksum PASS, GST exact to the cent on all five). Reconciliation: they total $7,996.86 ex-GST, 2.16x the 73140 SE2 balance of $3,703.03, so the monthly invoices bill the whole council and the Parks slice cannot be attributed. Correctly held unapplied; evidence limb stays AMBER pending the FY26 73140 ledger extract.</t>
   </si>
   <si>
     <t xml:space="preserve">1 Sight a sample of CV Check AP invoices to confirm evidence and tax limbs. 2 On sighting, clear to GREEN (no recode expected). 3 Pull the FY26 73140 ledger extract and match the five held Kinatico invoices by month and amount before any limb moves.</t>
@@ -232,7 +232,7 @@
     <t xml:space="preserve">n/a (no recode)</t>
   </si>
   <si>
-    <t xml:space="preserve">9-Jun-2026 (Kinatico intake held 11-Jun-2026)</t>
+    <t xml:space="preserve">17-Jun-2026 (intake disposition)</t>
   </si>
   <si>
     <t xml:space="preserve">73511</t>
@@ -352,7 +352,7 @@
     <t xml:space="preserve">Water Parks svc20802 $900 + Design&amp;Capital svc20191 $15,100 + s4090230 $38,242.75</t>
   </si>
   <si>
-    <t xml:space="preserve">A1 Strategy $15,100 (PO 708258) fails 73212 twice: four-element consultancy test met AND PO sits under the $20,000 floor; recode candidate to 73601 held (Tier 1 complete: 3 invoices + ABR x2 + ASIC, GST exact, hours recompute). Aust Care $630 invoice names PK000496, ledger charged PK000469 (PK recode candidate). GJ079210 -$66,183.82 one-sided Play Force move is the open dollar; ~$30,000 standing-order lines vendor-blind. | 11-Jun: GJ079210 backup SIGHTED - balanced 6-line PK move PK000035 to PK000022 (73123 $79,418 / 73212 $66,183.82 / 73211 $5,635), nets $0.00, direction correct; the $66,184 open dollar CLOSES as explained (narration crossover advisory; PK000510/511 not in maps). GJ076924 backup SIGHTED - 95-line balanced redistribution, $1,914 leg explained.</t>
+    <t xml:space="preserve">A1 Strategy $15,100 (PO 708258) fails 73212 twice: four-element consultancy test met AND PO sits under the $20,000 floor; recode candidate to 73601 held (Tier 1 complete: 3 invoices + ABR x2 + ASIC, GST exact, hours recompute). Aust Care $630 invoice names PK000496, ledger charged PK000469 (PK recode candidate). GJ079210 -$66,183.82 one-sided Play Force move is the open dollar; ~$30,000 standing-order lines vendor-blind. | 11-Jun: GJ079210 backup SIGHTED - balanced 6-line PK move PK000035 to PK000022 (73123 $79,418 / 73212 $66,183.82 / 73211 $5,635), nets $0.00, direction correct; the $66,184 open dollar CLOSES as explained (narration crossover advisory; PK000510/511 not in maps). GJ076924 backup SIGHTED - 95-line balanced redistribution, $1,914 leg explained. | 17-Jun: Materials reclassification PK000372 (svc 20551 Fuel Reduction Burn) evidenced - EMU INV-0367/0389/0395 ($26,414.08) SIGHTED as the 72111-&gt;73212 destination legs of posted journal XRef 934000000001 (directive-authorised, nets $0.00). See workstream 08_Materials_Recode_PK000372. Not a new recode; already posted.</t>
   </si>
   <si>
     <t xml:space="preserve">1 Spero rulings: A1 $15,100 73212-&gt;73601 (73603 alt); Aust Care PK000469-&gt;PK000496 $630. 2 GJ079210 + GJ076924 backups CLOSED 11-Jun-2026 (sighted, balanced, direction verified). 3 Vendor invoices for s4090230 standing orders (~$30,000). 4 Contracts vs the $20k floor: LCC-09-2022, Aust Care SO, Play Force. 5 Trace IPWEA $343.20 part-payment. 6 Confirm Anita Moore home service (OrgRisk invoice now corroborates Acting Parks Manager).</t>
@@ -451,7 +451,7 @@
     <t xml:space="preserve">Full account: 114 lines, 23 cost codes; section subsets verified (Natural Areas $116,963.24, Depots $23,626.58)</t>
   </si>
   <si>
-    <t xml:space="preserve">Reconciles to SE2 to the cent at the established scope ($236,378.27). 17-Jun-2026 evidence pass: 14 source invoices sighted exact to GL on the x1.1 test (Lockwise 2906937/2908705, TBM 97461/583/626/780, T2 3222869/3223786, Easy Signs 698933AU/713170AU, T&amp;H Levai INV-38877, 9016, Australasia 34828, 00735), all 8 distinct vendor ABN checksums PASS, GST math clean (no GST errors). Ausecology INV-4029 $8,480 + INV-4030 $6,360 sighted but $450 residual in GJ078960 and vendor ABN not on invoice (NARROWED). Evidence sighted now $208,815.65 of $236,378.27 (88.3%), $223,655.65 (94.6%) incl Ausecology narrowed. | 17-Jun MERGE: refreshed to 120 lines $267,532.19 (+6 P12 lines from the 17-Jun re-export, +$31,153.92) and 16 outstanding invoices sighted (+$66,404.23; Lothian, TBM, Ausecology, T2 Electrical, IDM, Radio Logan, Treescape, T&amp;H Levai, Wildlife Qld) - ported from PR-8.</t>
+    <t xml:space="preserve">Reconciles to SE2 to the cent at the established scope ($236,378.27). 17-Jun-2026 evidence pass: 14 source invoices sighted exact to GL on the x1.1 test (Lockwise 2906937/2908705, TBM 97461/583/626/780, T2 3222869/3223786, Easy Signs 698933AU/713170AU, T&amp;H Levai INV-38877, 9016, Australasia 34828, 00735), all 8 distinct vendor ABN checksums PASS, GST math clean (no GST errors). Ausecology INV-4029 $8,480 + INV-4030 $6,360 sighted but $450 residual in GJ078960 and vendor ABN not on invoice (NARROWED). Evidence sighted now $208,815.65 of $236,378.27 (88.3%), $223,655.65 (94.6%) incl Ausecology narrowed. | 17-Jun MERGE: refreshed to 120 lines $267,532.19 (+6 P12 lines from the 17-Jun re-export, +$31,153.92) and 16 outstanding invoices sighted (+$66,404.23; Lothian, TBM, Ausecology, T2 Electrical, IDM, Radio Logan, Treescape, T&amp;H Levai, Wildlife Qld) - ported from PR-8. | 17-Jun: Materials Journal intake closed two more evidence gaps - EWN INV-14768 ($375.00) and Wallum 00059013 ($276.80) now SIGHTED. Four gaps remain: Provac INV-00037183 ($2,050, no source), Telstra Dec-25 ($727.95, intake scan image-only), Wallum 00031055/79/85/86 ($1,668) and 00060617/47 ($493.40).</t>
   </si>
   <si>
     <t xml:space="preserve">Residual evidence GAP (~$5,505 quantified + EWN): small series 00059013/00031055/79/85/86/00060617/47 ($2,438.20), Provac INV-00037183 ($2,050), Telstra Dec-25 ($727.95), EWN INV-14768 (amount tbc); Ausecology $450 residual + vendor ABN. SCOPE: fresh 17-Jun export totals $267,532.19 vs register $236,378.27, delta $31,153.92 (suspected added P11/P12 lines incl 8 Org Risk Consulting WHS invoices INV-250714/811-813/910-913 present in intake but absent from 73211 ledger refs) - reconcile before changing scope. F1-F7 and candidate rulings still Spero's.</t>
@@ -461,9 +461,6 @@
   </si>
   <si>
     <t xml:space="preserve">n/a (no recode staged; findings held un-instructed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17-Jun-2026 (re-export +6 lines; 16 invoices sighted)</t>
   </si>
   <si>
     <t xml:space="preserve">62121/62125</t>
@@ -761,55 +758,55 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1773,7 +1770,7 @@
         <v>113</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1961,18 +1958,18 @@
         <v>146</v>
       </c>
       <c r="O21" s="5" t="s">
-        <v>147</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>149</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>150</v>
       </c>
       <c r="D22" s="6" t="n">
         <v>3711.73</v>
@@ -1996,16 +1993,16 @@
         <v>20</v>
       </c>
       <c r="K22" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="L22" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="L22" s="5" t="s">
+      <c r="M22" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="M22" s="5" t="s">
+      <c r="N22" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="N22" s="5" t="s">
-        <v>154</v>
       </c>
       <c r="O22" s="5" t="s">
         <v>121</v>
@@ -2013,13 +2010,13 @@
     </row>
     <row r="23" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>156</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>157</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>2944</v>
@@ -2043,16 +2040,16 @@
         <v>20</v>
       </c>
       <c r="K23" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="L23" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="L23" s="5" t="s">
+      <c r="M23" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="M23" s="5" t="s">
+      <c r="N23" s="5" t="s">
         <v>160</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>161</v>
       </c>
       <c r="O23" s="5" t="s">
         <v>121</v>
@@ -2060,13 +2057,13 @@
     </row>
     <row r="24" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>163</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>164</v>
       </c>
       <c r="D24" s="6" t="n">
         <v>7570.5</v>
@@ -2090,13 +2087,13 @@
         <v>20</v>
       </c>
       <c r="K24" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="L24" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="L24" s="5" t="s">
+      <c r="M24" s="5" t="s">
         <v>166</v>
-      </c>
-      <c r="M24" s="5" t="s">
-        <v>167</v>
       </c>
       <c r="N24" s="5" t="s">
         <v>77</v>
@@ -2107,13 +2104,13 @@
     </row>
     <row r="25" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="5" t="s">
         <v>169</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>170</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>642.14</v>
@@ -2137,16 +2134,16 @@
         <v>20</v>
       </c>
       <c r="K25" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="L25" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="L25" s="5" t="s">
+      <c r="M25" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="M25" s="5" t="s">
+      <c r="N25" s="5" t="s">
         <v>173</v>
-      </c>
-      <c r="N25" s="5" t="s">
-        <v>174</v>
       </c>
       <c r="O25" s="5" t="s">
         <v>121</v>
@@ -2154,13 +2151,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>177</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>21876.6</v>
@@ -2184,16 +2181,16 @@
         <v>20</v>
       </c>
       <c r="K26" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="L26" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="L26" s="5" t="s">
+      <c r="M26" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="M26" s="5" t="s">
+      <c r="N26" s="5" t="s">
         <v>180</v>
-      </c>
-      <c r="N26" s="5" t="s">
-        <v>181</v>
       </c>
       <c r="O26" s="5" t="s">
         <v>106</v>
@@ -2201,13 +2198,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>184</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>4861.7</v>
@@ -2231,24 +2228,24 @@
         <v>20</v>
       </c>
       <c r="K27" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="L27" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="L27" s="5" t="s">
+      <c r="M27" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="M27" s="5" t="s">
+      <c r="N27" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="N27" s="5" t="s">
+      <c r="O27" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="O27" s="5" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C28" s="12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D28" s="13" t="n">
         <f aca="false">SUM(D5:D27)</f>

--- a/00_Account_Review_Register.xlsx
+++ b/00_Account_Review_Register.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="191">
   <si>
     <t xml:space="preserve">LCC Parks 4090000  —  Account Review Register</t>
   </si>
@@ -115,7 +115,7 @@
     <t xml:space="preserve">RED</t>
   </si>
   <si>
-    <t xml:space="preserve">AP-invoice pass: $2,260.36 of $3,433.91 miscoded (Tennyson signage 72222, Ultimate PPE 72113, STIHL GTA 40 72315, INITIATOR chem 72112). Doc46 journal pass recodes $22,028 off 72111 across 11 NAs. The two OVERLAP (Tennyson 27577 $335 in both) and cannot be summed. EVIDENCE SIGHTED 9-Jun (Ultimate/Woodmans/Tennyson set C00267478, all ABNs PASS): 3 Trees-PK (20241/PK000055) recodes now STAGED in NA72111_GENJNL_Recode.txt - trousers PIK2270125 $292.09 and pants PIK2267644 $402.59 to 72113 PPE (partial, off mixed invoices), STIHL GTA 40 PIK2267816 $439.68 to 72315 parks P&amp;A (full); nets $0.00. Tennyson 27577 $335 evidence sighted, 72222 recode still HELD (Doc46 dedup). Woodmans 6429672 $54.41 correct in 72111. SET 2 staged 9-Jun (Motorcycles R Us PPE, svc 20301/PK000084, Spero directive): doc10286878 4 items $883.49 partial + doc10287279 pants $179.95 full = $1,063.44 ex to 72113. EVIDENCE GAP: Moto R Us invoices not packaged, ABN/GST unverified. Combined 72111 recode now $2,197.80 out ($1,758.12 to 72113, $439.68 to 72315), nets $0.00. SET 3 staged 9-Jun (scrap-plaque income reclass, Spero directive): -$448.00 ex "returned plaques for scrap" (SC10906) is sale income miscoded as a credit in 72111 expense on Depots PK000001; reclass to 64411 Sale of materials (revenue, unrestricted) on Cemeteries svc 20451/PK000402. Income reclass, signs inverted (Dr 72111 +448, Cr 64411 -448). Source doc SC10906 not sighted. Combined 72111 recode now 12 lines, net 72111 movement -$1,749.80, batch nets $0.00. SET 4 + DIRECTIVE 9-Jun: Spero standing directive - instructed lines override criteria and are PREPARED FOR JOURNAL (source-doc gaps audit-noted, not blocking). Set 4: TE004824 Officeworks 624206983 (ABN PASS, sighted) Posca PC5M markers $41.05 ex to 73563 stationery. 14-line recode now PREPARED; net 72111 -$1,790.85, nets $0.00 (72113 +1758.12, 72315 +439.68, 73563 +41.05, 64411 -448.00). Advisory: 3 OTTO desk risers $54.52 ex = 72313 candidate, not journalled pending instruction. | 10-Jun DEDUP CLOSED: the Doc46/AP overlap resolves to J22 only; 41 carried Doc46 items match 41 distinct ledger lines (37 full, 4 within-line partials, remainders $74.14 stay), zero collisions across all twelve journal streams (00_Doc46_AP_Dedup_10-Jun-2026.md).</t>
+    <t xml:space="preserve">AP-invoice pass: $2,260.36 of $3,433.91 miscoded (Tennyson signage 72222, Ultimate PPE 72113, STIHL GTA 40 72315, INITIATOR chem 72112). Doc46 journal pass recodes $22,028 off 72111 across 11 NAs. The two OVERLAP (Tennyson 27577 $335 in both) and cannot be summed. EVIDENCE SIGHTED 9-Jun (Ultimate/Woodmans/Tennyson set C00267478, all ABNs PASS): 3 Trees-PK (20241/PK000055) recodes now STAGED in NA72111_GENJNL_Recode.txt - trousers PIK2270125 $292.09 and pants PIK2267644 $402.59 to 72113 PPE (partial, off mixed invoices), STIHL GTA 40 PIK2267816 $439.68 to 72315 parks P&amp;A (full); nets $0.00. Tennyson 27577 $335 evidence sighted, 72222 recode still HELD (Doc46 dedup). Woodmans 6429672 $54.41 correct in 72111. SET 2 staged 9-Jun (Motorcycles R Us PPE, svc 20301/PK000084, Spero directive): doc10286878 4 items $883.49 partial + doc10287279 pants $179.95 full = $1,063.44 ex to 72113. EVIDENCE GAP: Moto R Us invoices not packaged, ABN/GST unverified. Combined 72111 recode now $2,197.80 out ($1,758.12 to 72113, $439.68 to 72315), nets $0.00. SET 3 staged 9-Jun (scrap-plaque income reclass, Spero directive): -$448.00 ex "returned plaques for scrap" (SC10906) is sale income miscoded as a credit in 72111 expense on Depots PK000001; reclass to 64411 Sale of materials (revenue, unrestricted) on Cemeteries svc 20451/PK000402. Income reclass, signs inverted (Dr 72111 +448, Cr 64411 -448). Source doc SC10906 not sighted. Combined 72111 recode now 12 lines, net 72111 movement -$1,749.80, batch nets $0.00. SET 4 + DIRECTIVE 9-Jun: Spero standing directive - instructed lines override criteria and are PREPARED FOR JOURNAL (source-doc gaps audit-noted, not blocking). Set 4: TE004824 Officeworks 624206983 (ABN PASS, sighted) Posca PC5M markers $41.05 ex to 73563 stationery. 14-line recode now PREPARED; net 72111 -$1,790.85, nets $0.00 (72113 +1758.12, 72315 +439.68, 73563 +41.05, 64411 -448.00). Advisory: 3 OTTO desk risers $54.52 ex = 72313 candidate, not journalled pending instruction. | 10-Jun DEDUP CLOSED: the Doc46/AP overlap resolves to J22 only; 41 carried Doc46 items match 41 distinct ledger lines (37 full, 4 within-line partials, remainders $74.14 stay), zero collisions across all twelve journal streams (00_Doc46_AP_Dedup_10-Jun-2026.md). | 18-Jun: full 72111 ledger PROVIDED (371 lines $68,112.06, 196 with attachments); large untested remainder now line-visible.</t>
   </si>
   <si>
     <t xml:space="preserve">1 Upload the 72111 streams (in the live journal). 2 Process GSTE-01 to 03 BAS adjustments ($69.50). 3 Spero scope call on the $63,621.56 untested remainder. Oasis/Pac Fire/Bunnings receipt GAPs closed 10-Jun-2026 (all four sighted, ABNs PASS, reconcile to the cent); Doc46 partial-recode remainders now content-known (PPE/decor candidates, un-instructed).</t>
@@ -202,7 +202,7 @@
     <t xml:space="preserve">N/A</t>
   </si>
   <si>
-    <t xml:space="preserve">3-Jun Reali PK split $1,059.76 confirmed subset (~4%). GJ SOURCE NOW SIGHTED (Document Reconstruction, doc 202603161072172000000001, ledger 26SLACT): a BALANCED multi-account recode batch (nets $0.00). Its 72114 block credits $10,650.27 from 1-20001-72114 narrated 'Institute of Public Works Engineering Au' (IPWEA) and DEBITS the same $10,650.27 across 16 service-level 72114 (Uniforms) PKs. CONCERN: if the $10,650.27 is a genuine IPWEA professional charge it should leave 72114 entirely (73542 Professional Membership most likely, or 73541 Conferences / 73544 Training), not be redistributed WITHIN Uniforms. Wider Reali standing-order set ($17,288.98) now provided (C00223414 zip), not yet worked. LIVE LISTING 9-Jun: 00_Uniform_Listing_72114.xlsx built from fresh TechOne export - full account 103 lines $26,236.42, 22 service codes. L1 Svc/PK 98 GREEN / 5 AMBER (off-home/unmapped); 57 of 103 lines have NO attachment (RED evidence); 46 have attachments (pending sighting). IPWEA -$10,650.27 (GJ078546) flagged to 73542. Reviewed-$ in this register stays the $1,059.76 Reali subset; the listing is the live per-line state.</t>
+    <t xml:space="preserve">3-Jun Reali PK split $1,059.76 confirmed subset (~4%). GJ SOURCE NOW SIGHTED (Document Reconstruction, doc 202603161072172000000001, ledger 26SLACT): a BALANCED multi-account recode batch (nets $0.00). Its 72114 block credits $10,650.27 from 1-20001-72114 narrated 'Institute of Public Works Engineering Au' (IPWEA) and DEBITS the same $10,650.27 across 16 service-level 72114 (Uniforms) PKs. CONCERN: if the $10,650.27 is a genuine IPWEA professional charge it should leave 72114 entirely (73542 Professional Membership most likely, or 73541 Conferences / 73544 Training), not be redistributed WITHIN Uniforms. Wider Reali standing-order set ($17,288.98) now provided (C00223414 zip), not yet worked. LIVE LISTING 9-Jun: 00_Uniform_Listing_72114.xlsx built from fresh TechOne export - full account 103 lines $26,236.42, 22 service codes. L1 Svc/PK 98 GREEN / 5 AMBER (off-home/unmapped); 57 of 103 lines have NO attachment (RED evidence); 46 have attachments (pending sighting). IPWEA -$10,650.27 (GJ078546) flagged to 73542. Reviewed-$ in this register stays the $1,059.76 Reali subset; the listing is the live per-line state. | 18-Jun: full 72114 ledger PROVIDED (112 lines $27,590.02, 51 with attachments); the $25,176.66 untested remainder is now line-visible for review.</t>
   </si>
   <si>
     <t xml:space="preserve">1 Confirm whether the reconstruction batch is POSTED or PROPOSED; if posted, the IPWEA $10,650.27 is already spread across Uniforms service PKs. 2 Obtain the underlying IPWEA invoice to confirm nature (membership vs conference vs training) and set destination (73542/73541/73544); it should not sit in 72114. 3 Work the now-provided Reali set at full scope. 4 Confirm net-movement vs full-reversal format. Same batch also shows other apparent miscodes outside scope (e.g. Empire Office Furniture $4,300 in 73544 Training). | 10-Jun: Reali Mar-2026 invoice sighted (GSTE-06 $0.01 note); officer split basis captured, not journalled</t>
@@ -220,7 +220,7 @@
     <t xml:space="preserve">CV Check PK000001 svc20001</t>
   </si>
   <si>
-    <t xml:space="preserve">Carried from 3-Jun pass. 21 lines, single vendor (CV Check), narration consistent, NA matches chart definition; coding correct. $58.02 GJ EOY reversal normal. Tier-3 sighting only: AP invoices not sighted, so evidence and tax limbs remain open. 11-Jun-2026: five Kinatico Limited tax invoices received in intake (ABN 25 111 728 842, PO 801790, monthly pre-employment screening; Kinatico is the CVCheck parent): P00075671 Jul-2025, P00081314 Dec-2025, P00082255 Jan-2026, P00083290 Feb-2026, P00086890 May-2026. All five AP document numbers searched across every 11-Jun ledger export: zero hits. Held unapplied in 07_Intake_Held_Kinatico/ per the evidence rule; no limb moves until matched to 73140 ledger lines. | 17-Jun: five held Kinatico invoices VERIFIED (ABN 25 111 728 842 checksum PASS, GST exact to the cent on all five). Reconciliation: they total $7,996.86 ex-GST, 2.16x the 73140 SE2 balance of $3,703.03, so the monthly invoices bill the whole council and the Parks slice cannot be attributed. Correctly held unapplied; evidence limb stays AMBER pending the FY26 73140 ledger extract.</t>
+    <t xml:space="preserve">Carried from 3-Jun pass. 21 lines, single vendor (CV Check), narration consistent, NA matches chart definition; coding correct. $58.02 GJ EOY reversal normal. Tier-3 sighting only: AP invoices not sighted, so evidence and tax limbs remain open. 11-Jun-2026: five Kinatico Limited tax invoices received in intake (ABN 25 111 728 842, PO 801790, monthly pre-employment screening; Kinatico is the CVCheck parent): P00075671 Jul-2025, P00081314 Dec-2025, P00082255 Jan-2026, P00083290 Feb-2026, P00086890 May-2026. All five AP document numbers searched across every 11-Jun ledger export: zero hits. Held unapplied in 07_Intake_Held_Kinatico/ per the evidence rule; no limb moves until matched to 73140 ledger lines. | 17-Jun: five held Kinatico invoices VERIFIED (ABN 25 111 728 842 checksum PASS, GST exact to the cent on all five). Reconciliation: they total $7,996.86 ex-GST, 2.16x the 73140 SE2 balance of $3,703.03, so the monthly invoices bill the whole council and the Parks slice cannot be attributed. Correctly held unapplied; evidence limb stays AMBER pending the FY26 73140 ledger extract. | 18-Jun: 73140 ledger SIGHTED, reconciles $3,703.03 exact (22 lines, all att=Y). Two vendors found - CV Check/Kinatico and JobFit standing order. The five held Kinatico invoices ATTRIBUTED to their ledger lines by P-number (Parks slice $632.09; the invoices bill the whole council). Remaining evidence: 6 more CV Check months + 10 JobFit lines, all att=Y in TechOne.</t>
   </si>
   <si>
     <t xml:space="preserve">1 Sight a sample of CV Check AP invoices to confirm evidence and tax limbs. 2 On sighting, clear to GREEN (no recode expected). 3 Pull the FY26 73140 ledger extract and match the five held Kinatico invoices by month and amount before any limb moves.</t>
@@ -232,138 +232,141 @@
     <t xml:space="preserve">n/a (no recode)</t>
   </si>
   <si>
+    <t xml:space="preserve">18-Jun-2026 (ledger sighted; Kinatico attributed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entertainment &amp; Hospitality (FBT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 svc codes (Natural Areas x3, Depots, Mgmt, Planning, Park Services); 126 lines incl Finance 50/50 batch pairs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full account $5,384.57 ex-GST net of Finance FBT batch pairs (58 lines net $0.00, set aside; 2 AP003801 re-posts live). Annotated export = claims, not Tier 1; candidates quantified, NOT journalled: $762.33 to 73512 (amenity $334.71, non-employee $301.71, training catering $125.91), Warnholtz $744.30 to 73544, $23.56 utensils to 72111; Daily Blooms $88.14 customer-gift query. STAY-FBT $3,664.79 incl unsighted INV-9747 $2,445.45. One $4.18 doesnt-reconcile RED; $97.27 unannotated. | 11-Jun: INV-9747 SIGHTED - Greenbank Services Club (ABN 64 442 003 715 PASS, ABR active + GST reg, business name matches), EOY celebration 3-Dec-2025, food $2,690.00 incl = GL $2,445.45 x 1.1 exact, GST disclosure exact. STAY-FBT verdict now on Tier 1. Residual traces: $700 room hire payment and $200 bond return.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Spero ruling on the 73512/73544/72111 candidate set + Daily Blooms class 2 Sight INV-9747 ($2,445.45, vendor unidentified) and Warnholtz 001 3 Identify Hoffmann/Bahry/Warnholtz/Salisnew (not in employee map); confirm Mann/Rosmarin sections 4 Receipts for the PCard food population (GST-free mix) 5 Classify 4 unannotated lines | 11-Jun: INV-9747 sighted and vendor identified (item 2 partially closed; Warnholtz 001 remains). New: trace the $700 room hire payment and $200 bond return on the Greenbank engagement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA73511_Evidence/ (annotated ledger extract; no receipts sighted)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a (no recode staged)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10-Jun-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCB milk standing order PO 709655, PK000001 svc20151 Depots (57 PUR + 4 GJ075544 lines) + Raj Aggarwal bond pair (nets $0.00)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$1,854.70 of $1,854.70 (100%) of the milk spend miscoded to 73128 last-resort services; goods purchase belongs in 73512 Entertainment &amp; Hospitality Non-FBT (recode instructed by Spero 10-Jun-2026). All 50 unique invoices and the bond refund documents sighted; account reconciles to the ledger with no residual. 16 GST errors confirmed, $61.11 ITC over-claimed Jun-2025 to mid-Sep-2025 (corrected at source from INV-399504), recorded GSTE-07 to GSTE-22; bond refund net-nil GST timing note $272.73 recorded GSTE-23. ABR live record 10-Jun-2026 confirms TCB Distributors Pty Ltd active and GST registered. Incl-GST column carries the GST-free invoice value $1,915.81 (GL $1,854.70 + $61.11 under-keyed base), not ex x 1.1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Upload NA73128_GENJNL_Recode.txt (122 lines, 61 pairs, nets $0.00, direction verified). 2 Process the $61.11 BAS adjustment (GSTE-07 to GSTE-22); no GENJNL movement. 3 Package the 56 per-line evidence PDFs into NA73128_Evidence/ (sighted 10-Jun-2026, SHA-256 fingerprints held in NA73128_Workstream_Manifest_10-Jun-2026.csv; only the compressed second-intake binder is carried this bundle).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA73128_Evidence/ (second-intake binder C00216123; ledger extract; ABR record); NA73128_Evidence_Manifest.csv (59 rows, no GAP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN-23167 (journal-ready, Spero 10-Jun-2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other Fees &amp; Charges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two lines: QUT parking PK000087 svc20001 + blue card recode-in PK000075 svc20411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$34.55 of $139.25 (24.8%) miscoded: QUT visitor parking belongs in 73531 Local Travel SEQ (GJ078933 precedent). Blue card $104.70 correctly recoded in from 73544; original TE004496 receipt unsighted. | 11-Jun: TE004496 receipt SIGHTED - Blue Card Services 56213618922, Preussner renewal $104.70, Div 81 GST exempt, booked gross with no ITC, Dyba PCard, slip coded PK000075-73544. Evidence gap CLOSED. | 17-Jun: manifest-vs-register conflict RECONCILED - the TE004496 Blue Card receipt (56213618922, $104.70 Div 81 exempt) is held and SIGHTED (NA73433_L02, SHA 95f8b186 verified); a stale duplicate GAP row was removed from the manifest. Both 73433 lines (TE005281, TE004496) now sighted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Upload NA73433_GENJNL_Recode.txt (in the live journal; 73433-&gt;73531 $34.55, PK000087, nets $0.00, direction verified). 2 TE004496 blue card receipt SIGHTED 11-Jun-2026 (gap closed). 3 Confirm TE005281 cardholder.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA73433_Evidence/ (QUT receipt TE005281, hash-verified)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN-23167 (journal-ready, Spero 10-Jun-2026; NA73433 stream in the live journal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entertainment &amp; Hospitality Non-FBT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122 lines, 7 svc codes; volunteer reimbursements + FBT batch micro-lines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account reconciles to the cent. 5 of 6 volunteer reimbursements fully evidenced (Hoffmann x3, Preussner x2, GST exact, identity matched); Warnholtz AP003847 asymmetry resolved (GSTE-24). Open: Quote 5468 $1,656.50 vendor unknown (largest unevidenced line), Salisnew ~$234, ~100 FBT-batch micro-lines.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Sight 12052026 Preussner receipt $27.79. 2 Identify Quote 5468 vendor + invoice. 3 Salisnew receipts x6. 4 Micro-line population: pcard docs OR Spero waiver. 5 Confirm TE005497/AP003877 $97.00+$7.90 split.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA73512_Evidence/ (5 receipts + 2 identity docs, hash-verified; identity docs carry full bank details, restrict to folder)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training &amp; Development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full account: 41 lines, $69,232.16; 17 vendor docs + back-charges intake sighted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Account reconciles. 21 references evidenced incl Whitehead $18,750, Fire Mgmt $10,500, Bendelta $8,966.28 (consultancy recode candidate to 73601), BAL $1,767 (73541 candidate; HLW dossier sighted, tax invoice outstanding), PSIA narration error. GST errors: Blue Dog $11.73 (GSTE-25), Barter $9.52 (GSTE-26), OIR $8.76 corrected (GSTE-27). 11-Jun: PK-split recode STAGED $2,131.46 (GJ079650 chargebacks $949.64 + ACCA split $1,181.82, 9 lines, nets $0.00, re-verified); Pryor/Hambly held; Preussner GJ078933 reopened as a destination query (73545 vs 7B411 on the $931.20 leg). | 11-Jun: GJ076597 backup + L&amp;D email SIGHTED (non-attendance recharge batch, nets $0.00; Pryor $214.00 and Hambly $294.42 evidenced as L&amp;D non-attendance, home-PK ruling remains). OIR source receipt SIGHTED: licensee Renee Hoyle, $96.35, PK000383 ParkCare; Hood audit email corroborates GSTE-27. | 17-Jun: SIX journal backups SIGHTED (L23-L28), each a balanced Document Reconstruction netting $0.00 (IJ074222, GJ078710, GJ078895, GJ077155, GJ079267, GJ078296); journal-backup gap CLOSED. ACCA INV-11404 deficiency was stale: invoice held at L10 since 10-Jun (SHA 6126cdf2); EVID overlay lines 159-161 relinked to EVID-0148 from a stale placeholder (matcher miss corrected). Internal journals post cross-ledger to 26PSLACT/26RMACT/WW03; NA 73544 consistent throughout.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Upload NA73544_GENJNL_Recode.txt (in the live journal). 2 Spero rulings: Bendelta-&gt;73601 $8,966.28; BAL 73541-vs-73544 $1,767; Warnholtz concurrence; Pryor PK000044-vs-PK000003 $214.00; Hambly $294.42 (not in map); Preussner destination query. 3 Sight: HLW tax invoice, OIR source receipt, 7 journal backups ~$11,100. 4 Confirm Moore/Moir/Funk services (EOM report). 5 BAS: GSTE-25/26 reversals. | 11-Jun: journal backups now 6 outstanding (~$10,600: IJ074222, GJ078710, GJ078895, GJ077155, GJ079267, GJ078296); OIR source receipt CLOSED. | 17-Jun: item 3 journal backups (6) CLOSED at L23-L28; ACCA deficiency closed (relinked, was stale). Residual on item 3: HLW (BAL) compliant tax invoice still outstanding (tax limb AMBER). Items 1,2,4,5 unchanged (Bendelta/BAL/Pryor/Hambly/Preussner rulings still with Spero; BAL workshop receipt $1,943.70 in intake does NOT match $1,767 TE004334 - reconcile before it closes the 73541 candidate).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA73544_Evidence/ (46 files: 17-Jun added L23-L28 journal backups, SHA-verified)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CN-23167 (journal-ready, Spero 11-Jun-2026; NA73544 PK-split stream in the live journal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17-Jun-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Major Contracts (3 section exports)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water Parks svc20802 $900 + Design&amp;Capital svc20191 $15,100 + s4090230 $38,242.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1 Strategy $15,100 (PO 708258) fails 73212 twice: four-element consultancy test met AND PO sits under the $20,000 floor; recode candidate to 73601 held (Tier 1 complete: 3 invoices + ABR x2 + ASIC, GST exact, hours recompute). Aust Care $630 invoice names PK000496, ledger charged PK000469 (PK recode candidate). GJ079210 -$66,183.82 one-sided Play Force move is the open dollar; ~$30,000 standing-order lines vendor-blind. | 11-Jun: GJ079210 backup SIGHTED - balanced 6-line PK move PK000035 to PK000022 (73123 $79,418 / 73212 $66,183.82 / 73211 $5,635), nets $0.00, direction correct; the $66,184 open dollar CLOSES as explained (narration crossover advisory; PK000510/511 not in maps). GJ076924 backup SIGHTED - 95-line balanced redistribution, $1,914 leg explained. | 17-Jun: Materials reclassification PK000372 (svc 20551 Fuel Reduction Burn) evidenced - EMU INV-0367/0389/0395 ($26,414.08) SIGHTED as the 72111-&gt;73212 destination legs of posted journal XRef 934000000001 (directive-authorised, nets $0.00). See workstream 08_Materials_Recode_PK000372. Not a new recode; already posted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 Spero rulings: A1 $15,100 73212-&gt;73601 (73603 alt); Aust Care PK000469-&gt;PK000496 $630. 2 GJ079210 + GJ076924 backups CLOSED 11-Jun-2026 (sighted, balanced, direction verified). 3 Vendor invoices for s4090230 standing orders (~$30,000). 4 Contracts vs the $20k floor: LCC-09-2022, Aust Care SO, Play Force. 5 Trace IPWEA $343.20 part-payment. 6 Confirm Anita Moore home service (OrgRisk invoice now corroborates Acting Parks Manager).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA73212_Evidence/ (8 files, hash-verified)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a (candidates held, no recode staged)</t>
+  </si>
+  <si>
     <t xml:space="preserve">17-Jun-2026 (intake disposition)</t>
   </si>
   <si>
-    <t xml:space="preserve">73511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entertainment &amp; Hospitality (FBT)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 svc codes (Natural Areas x3, Depots, Mgmt, Planning, Park Services); 126 lines incl Finance 50/50 batch pairs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full account $5,384.57 ex-GST net of Finance FBT batch pairs (58 lines net $0.00, set aside; 2 AP003801 re-posts live). Annotated export = claims, not Tier 1; candidates quantified, NOT journalled: $762.33 to 73512 (amenity $334.71, non-employee $301.71, training catering $125.91), Warnholtz $744.30 to 73544, $23.56 utensils to 72111; Daily Blooms $88.14 customer-gift query. STAY-FBT $3,664.79 incl unsighted INV-9747 $2,445.45. One $4.18 doesnt-reconcile RED; $97.27 unannotated. | 11-Jun: INV-9747 SIGHTED - Greenbank Services Club (ABN 64 442 003 715 PASS, ABR active + GST reg, business name matches), EOY celebration 3-Dec-2025, food $2,690.00 incl = GL $2,445.45 x 1.1 exact, GST disclosure exact. STAY-FBT verdict now on Tier 1. Residual traces: $700 room hire payment and $200 bond return.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Spero ruling on the 73512/73544/72111 candidate set + Daily Blooms class 2 Sight INV-9747 ($2,445.45, vendor unidentified) and Warnholtz 001 3 Identify Hoffmann/Bahry/Warnholtz/Salisnew (not in employee map); confirm Mann/Rosmarin sections 4 Receipts for the PCard food population (GST-free mix) 5 Classify 4 unannotated lines | 11-Jun: INV-9747 sighted and vendor identified (item 2 partially closed; Warnholtz 001 remains). New: trace the $700 room hire payment and $200 bond return on the Greenbank engagement.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA73511_Evidence/ (annotated ledger extract; no receipts sighted)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n/a (no recode staged)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10-Jun-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCB milk standing order PO 709655, PK000001 svc20151 Depots (57 PUR + 4 GJ075544 lines) + Raj Aggarwal bond pair (nets $0.00)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$1,854.70 of $1,854.70 (100%) of the milk spend miscoded to 73128 last-resort services; goods purchase belongs in 73512 Entertainment &amp; Hospitality Non-FBT (recode instructed by Spero 10-Jun-2026). All 50 unique invoices and the bond refund documents sighted; account reconciles to the ledger with no residual. 16 GST errors confirmed, $61.11 ITC over-claimed Jun-2025 to mid-Sep-2025 (corrected at source from INV-399504), recorded GSTE-07 to GSTE-22; bond refund net-nil GST timing note $272.73 recorded GSTE-23. ABR live record 10-Jun-2026 confirms TCB Distributors Pty Ltd active and GST registered. Incl-GST column carries the GST-free invoice value $1,915.81 (GL $1,854.70 + $61.11 under-keyed base), not ex x 1.1.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Upload NA73128_GENJNL_Recode.txt (122 lines, 61 pairs, nets $0.00, direction verified). 2 Process the $61.11 BAS adjustment (GSTE-07 to GSTE-22); no GENJNL movement. 3 Package the 56 per-line evidence PDFs into NA73128_Evidence/ (sighted 10-Jun-2026, SHA-256 fingerprints held in NA73128_Workstream_Manifest_10-Jun-2026.csv; only the compressed second-intake binder is carried this bundle).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA73128_Evidence/ (second-intake binder C00216123; ledger extract; ABR record); NA73128_Evidence_Manifest.csv (59 rows, no GAP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CN-23167 (journal-ready, Spero 10-Jun-2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other Fees &amp; Charges</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two lines: QUT parking PK000087 svc20001 + blue card recode-in PK000075 svc20411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$34.55 of $139.25 (24.8%) miscoded: QUT visitor parking belongs in 73531 Local Travel SEQ (GJ078933 precedent). Blue card $104.70 correctly recoded in from 73544; original TE004496 receipt unsighted. | 11-Jun: TE004496 receipt SIGHTED - Blue Card Services 56213618922, Preussner renewal $104.70, Div 81 GST exempt, booked gross with no ITC, Dyba PCard, slip coded PK000075-73544. Evidence gap CLOSED.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Upload NA73433_GENJNL_Recode.txt (in the live journal; 73433-&gt;73531 $34.55, PK000087, nets $0.00, direction verified). 2 TE004496 blue card receipt SIGHTED 11-Jun-2026 (gap closed). 3 Confirm TE005281 cardholder.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA73433_Evidence/ (QUT receipt TE005281, hash-verified)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CN-23167 (journal-ready, Spero 10-Jun-2026; NA73433 stream in the live journal)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entertainment &amp; Hospitality Non-FBT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">122 lines, 7 svc codes; volunteer reimbursements + FBT batch micro-lines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account reconciles to the cent. 5 of 6 volunteer reimbursements fully evidenced (Hoffmann x3, Preussner x2, GST exact, identity matched); Warnholtz AP003847 asymmetry resolved (GSTE-24). Open: Quote 5468 $1,656.50 vendor unknown (largest unevidenced line), Salisnew ~$234, ~100 FBT-batch micro-lines.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Sight 12052026 Preussner receipt $27.79. 2 Identify Quote 5468 vendor + invoice. 3 Salisnew receipts x6. 4 Micro-line population: pcard docs OR Spero waiver. 5 Confirm TE005497/AP003877 $97.00+$7.90 split.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA73512_Evidence/ (5 receipts + 2 identity docs, hash-verified; identity docs carry full bank details, restrict to folder)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Training &amp; Development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full account: 41 lines, $69,232.16; 17 vendor docs + back-charges intake sighted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Account reconciles. 21 references evidenced incl Whitehead $18,750, Fire Mgmt $10,500, Bendelta $8,966.28 (consultancy recode candidate to 73601), BAL $1,767 (73541 candidate; HLW dossier sighted, tax invoice outstanding), PSIA narration error. GST errors: Blue Dog $11.73 (GSTE-25), Barter $9.52 (GSTE-26), OIR $8.76 corrected (GSTE-27). 11-Jun: PK-split recode STAGED $2,131.46 (GJ079650 chargebacks $949.64 + ACCA split $1,181.82, 9 lines, nets $0.00, re-verified); Pryor/Hambly held; Preussner GJ078933 reopened as a destination query (73545 vs 7B411 on the $931.20 leg). | 11-Jun: GJ076597 backup + L&amp;D email SIGHTED (non-attendance recharge batch, nets $0.00; Pryor $214.00 and Hambly $294.42 evidenced as L&amp;D non-attendance, home-PK ruling remains). OIR source receipt SIGHTED: licensee Renee Hoyle, $96.35, PK000383 ParkCare; Hood audit email corroborates GSTE-27. | 17-Jun: SIX journal backups SIGHTED (L23-L28), each a balanced Document Reconstruction netting $0.00 (IJ074222, GJ078710, GJ078895, GJ077155, GJ079267, GJ078296); journal-backup gap CLOSED. ACCA INV-11404 deficiency was stale: invoice held at L10 since 10-Jun (SHA 6126cdf2); EVID overlay lines 159-161 relinked to EVID-0148 from a stale placeholder (matcher miss corrected). Internal journals post cross-ledger to 26PSLACT/26RMACT/WW03; NA 73544 consistent throughout.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Upload NA73544_GENJNL_Recode.txt (in the live journal). 2 Spero rulings: Bendelta-&gt;73601 $8,966.28; BAL 73541-vs-73544 $1,767; Warnholtz concurrence; Pryor PK000044-vs-PK000003 $214.00; Hambly $294.42 (not in map); Preussner destination query. 3 Sight: HLW tax invoice, OIR source receipt, 7 journal backups ~$11,100. 4 Confirm Moore/Moir/Funk services (EOM report). 5 BAS: GSTE-25/26 reversals. | 11-Jun: journal backups now 6 outstanding (~$10,600: IJ074222, GJ078710, GJ078895, GJ077155, GJ079267, GJ078296); OIR source receipt CLOSED. | 17-Jun: item 3 journal backups (6) CLOSED at L23-L28; ACCA deficiency closed (relinked, was stale). Residual on item 3: HLW (BAL) compliant tax invoice still outstanding (tax limb AMBER). Items 1,2,4,5 unchanged (Bendelta/BAL/Pryor/Hambly/Preussner rulings still with Spero; BAL workshop receipt $1,943.70 in intake does NOT match $1,767 TE004334 - reconcile before it closes the 73541 candidate).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA73544_Evidence/ (46 files: 17-Jun added L23-L28 journal backups, SHA-verified)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CN-23167 (journal-ready, Spero 11-Jun-2026; NA73544 PK-split stream in the live journal)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17-Jun-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Major Contracts (3 section exports)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water Parks svc20802 $900 + Design&amp;Capital svc20191 $15,100 + s4090230 $38,242.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A1 Strategy $15,100 (PO 708258) fails 73212 twice: four-element consultancy test met AND PO sits under the $20,000 floor; recode candidate to 73601 held (Tier 1 complete: 3 invoices + ABR x2 + ASIC, GST exact, hours recompute). Aust Care $630 invoice names PK000496, ledger charged PK000469 (PK recode candidate). GJ079210 -$66,183.82 one-sided Play Force move is the open dollar; ~$30,000 standing-order lines vendor-blind. | 11-Jun: GJ079210 backup SIGHTED - balanced 6-line PK move PK000035 to PK000022 (73123 $79,418 / 73212 $66,183.82 / 73211 $5,635), nets $0.00, direction correct; the $66,184 open dollar CLOSES as explained (narration crossover advisory; PK000510/511 not in maps). GJ076924 backup SIGHTED - 95-line balanced redistribution, $1,914 leg explained. | 17-Jun: Materials reclassification PK000372 (svc 20551 Fuel Reduction Burn) evidenced - EMU INV-0367/0389/0395 ($26,414.08) SIGHTED as the 72111-&gt;73212 destination legs of posted journal XRef 934000000001 (directive-authorised, nets $0.00). See workstream 08_Materials_Recode_PK000372. Not a new recode; already posted.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 Spero rulings: A1 $15,100 73212-&gt;73601 (73603 alt); Aust Care PK000469-&gt;PK000496 $630. 2 GJ079210 + GJ076924 backups CLOSED 11-Jun-2026 (sighted, balanced, direction verified). 3 Vendor invoices for s4090230 standing orders (~$30,000). 4 Contracts vs the $20k floor: LCC-09-2022, Aust Care SO, Play Force. 5 Trace IPWEA $343.20 part-payment. 6 Confirm Anita Moore home service (OrgRisk invoice now corroborates Acting Parks Manager).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NA73212_Evidence/ (8 files, hash-verified)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n/a (candidates held, no recode staged)</t>
-  </si>
-  <si>
     <t xml:space="preserve">73215</t>
   </si>
   <si>
@@ -574,7 +577,7 @@
     <t xml:space="preserve">Whole-branch immunisation on NatAreas PK000432 (svc 20318); 70 lines P2-P12</t>
   </si>
   <si>
-    <t xml:space="preserve">Internal immunisation recharge, $4,861.70 ex-GST over 70 lines P2-P12, miscoded at PK level: Internal_Medical.XLSM 'Lookup Values' row 23 maps the whole 4090000 Parks branch to one ledger line PK000432-7B213 (svc 20318 Natural Areas), so every Parks employee's immunisation charge lands on Natural Areas regardless of section. Natural account 7B213 and the per-line amounts are not in dispute (L2 GREEN); the defect is Limb 1 PK attribution. Staged svc-PK split reallocates $3,799.50 over 17 pairs to home PKs (Park Maintenance PK000003/PK000012, Rangers PK000084, Trees PK000433, Park Services PK000435, NatAreas PK000431), nets $0.00, source PK000432 signed sum -$3,799.50, every pair passes pk_validator and the 40-char cap. Stays on PK000432: $541.30 (James Lloyd-Jones $338.30, Renee Hoyle $82.00 correct; Arno Schneider $121.00 held pending section). Off-branch (not Parks) $520.90 incl a $146.30 duplicate, cross-branch, needs Finance. Sonya Karlsson/Christian De Leon/Gregory Cavell are Spero-instructed placements (not on the roster). Internal account: no GST event, L4 n/a. SE2 reconciliation not yet performed; no account-level GREEN until it ties.</t>
+    <t xml:space="preserve">Internal immunisation recharge, $4,861.70 ex-GST over 70 lines P2-P12, miscoded at PK level: Internal_Medical.XLSM 'Lookup Values' row 23 maps the whole 4090000 Parks branch to one ledger line PK000432-7B213 (svc 20318 Natural Areas), so every Parks employee's immunisation charge lands on Natural Areas regardless of section. Natural account 7B213 and the per-line amounts are not in dispute (L2 GREEN); the defect is Limb 1 PK attribution. Staged svc-PK split reallocates $3,799.50 over 17 pairs to home PKs (Park Maintenance PK000003/PK000012, Rangers PK000084, Trees PK000433, Park Services PK000435, NatAreas PK000431), nets $0.00, source PK000432 signed sum -$3,799.50, every pair passes pk_validator and the 40-char cap. Stays on PK000432: $541.30 (James Lloyd-Jones $338.30, Renee Hoyle $82.00 correct; Arno Schneider $121.00 held pending section). Off-branch (not Parks) $520.90 incl a $146.30 duplicate, cross-branch, needs Finance. Sonya Karlsson/Christian De Leon/Gregory Cavell are Spero-instructed placements (not on the roster). Internal account: no GST event, L4 n/a. SE2 reconciliation not yet performed; no account-level GREEN until it ties. | 18-Jun: EVIDENCE CITED. Parks 4090000 7B213 ledger export sighted - 70 lines reconcile $4,861.70 exact, all 11 source IJs match line-for-line; Internal Immunisation Services Journal (per-person/vaccine source) also held. Evidence limb GREEN. Tax limb n/a (internal charge).</t>
   </si>
   <si>
     <t xml:space="preserve">1 Supply Arno Schneider's section to add his pair to the recode. 2 Confirm whether Park Maintenance staff resolve to PK000012 vs PK000003 by substantive position. 3 Hand the off-branch SL reversal draft and the $146.30 duplicate query to Finance. 4 Fix Internal_Medical.XLSM row 23 to a per-section Parks lookup so the miscode stops recurring. 5 Sight the immunisation IJ backings (evidence GAP, all 70 lines unsighted). 6 Tie the export to SE2 to the cent.</t>
@@ -586,7 +589,7 @@
     <t xml:space="preserve">CN-23167 (journal-ready, Spero; $3,799.50 svc-PK split, 17 pairs, nets $0.00)</t>
   </si>
   <si>
-    <t xml:space="preserve">16-Jun-2026</t>
+    <t xml:space="preserve">18-Jun-2026 (70 lines cited)</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL reviewed $ (this register)</t>
@@ -1607,8 +1610,8 @@
       <c r="G14" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="H14" s="9" t="s">
-        <v>20</v>
+      <c r="H14" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>20</v>
@@ -1770,18 +1773,18 @@
         <v>113</v>
       </c>
       <c r="O17" s="5" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>4739</v>
@@ -1805,30 +1808,30 @@
         <v>20</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O18" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="137.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>46003.66</v>
@@ -1852,30 +1855,30 @@
         <v>29</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O19" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="157.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>0</v>
@@ -1884,45 +1887,45 @@
         <v>0</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O20" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>267532.19</v>
@@ -1946,30 +1949,30 @@
         <v>20</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O21" s="5" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="178.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D22" s="6" t="n">
         <v>3711.73</v>
@@ -1993,30 +1996,30 @@
         <v>20</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O22" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="126.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>2944</v>
@@ -2034,36 +2037,36 @@
         <v>20</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>20</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O23" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="116.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D24" s="6" t="n">
         <v>7570.5</v>
@@ -2081,36 +2084,36 @@
         <v>20</v>
       </c>
       <c r="I24" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>20</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N24" s="5" t="s">
         <v>77</v>
       </c>
       <c r="O24" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>642.14</v>
@@ -2134,30 +2137,30 @@
         <v>20</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N25" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O25" s="5" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>21876.6</v>
@@ -2181,16 +2184,16 @@
         <v>20</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N26" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O26" s="5" t="s">
         <v>106</v>
@@ -2198,13 +2201,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>4861.7</v>
@@ -2218,34 +2221,34 @@
       <c r="G27" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H27" s="9" t="s">
-        <v>20</v>
+      <c r="H27" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J27" s="9" t="s">
         <v>20</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N27" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O27" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C28" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D28" s="13" t="n">
         <f aca="false">SUM(D5:D27)</f>

--- a/00_Account_Review_Register.xlsx
+++ b/00_Account_Review_Register.xlsx
@@ -1743,7 +1743,7 @@
       </c>
       <c r="K20" s="19" t="inlineStr">
         <is>
-          <t>OPENED ONLY, no limb rated. Export sums $3,951,109.43 vs SE2 (8-Jun) $3,900,770.79: gap $50,338.64 unresolved (suspected export row duplication - 365 exact-duplicate rows $20,201.46, accrual legs appearing in triplicate - and/or 8-to-11-Jun P12 timing). Per session rule no conclusions until reconciled, so Reviewed-$ stays $0. Profile: AP $3,971,119.30 over 3,339 rows; GL net -$23,019.35 (self-reversing EOM accruals + 2 Pool Shop recodes out); top services 20392 $1,304,200 and 20481 $1,273,366 (65% of dollars); 12 no-attachment rows $321,060.51. GJ079210 condition-assessment legs ($79,418 pair) net zero inside the account, backup sighted. Known trap: 73123/73212 reclassification pair, read combined. Sub-extracts s4090210 ($2,985.97, small Depots preventative maintenance, plausibly clean) and s4090230 ($31,995.72) on hand.</t>
+          <t>OPENED ONLY, no limb rated. Export sums $3,951,109.43 vs SE2 (8-Jun) $3,900,770.79: gap $50,338.64 unresolved (suspected export row duplication - 365 exact-duplicate rows $20,201.46, accrual legs appearing in triplicate - and/or 8-to-11-Jun P12 timing). Per session rule no conclusions until reconciled, so Reviewed-$ stays $0. Profile: AP $3,971,119.30 over 3,339 rows; GL net -$23,019.35 (self-reversing EOM accruals + 2 Pool Shop recodes out); top services 20392 $1,304,200 and 20481 $1,273,366 (65% of dollars); 12 no-attachment rows $321,060.51. GJ079210 condition-assessment legs ($79,418 pair) net zero inside the account, backup sighted. Known trap: 73123/73212 reclassification pair, read combined. Sub-extracts s4090210 ($2,985.97, small Depots preventative maintenance, plausibly clean) and s4090230 ($31,995.72) on hand. | 18-Jun: reconciliation NARROWED. Export $3,951,109.43 confirmed exact (3,776 lines). Found $18,342.92 genuine duplicate inflation (333 excess lines) + duplicate journal pair RJ013539/RJ013556 (net zero, data-quality flag) + P12 timing -$23,785.70. Residual ~$31,995.72 needs GL confirmation of SE2 exclusions (SE2 is summary-only, no line detail). See 00_Analysis_Findings_PKmap_73123_18-Jun-2026.md.</t>
         </is>
       </c>
       <c r="L20" s="19" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="O20" s="19" t="inlineStr">
         <is>
-          <t>11-Jun-2026 (opened)</t>
+          <t>18-Jun-2026 (reconciliation narrowed)</t>
         </is>
       </c>
     </row>

--- a/00_Account_Review_Register.xlsx
+++ b/00_Account_Review_Register.xlsx
@@ -1780,14 +1780,14 @@
       </c>
       <c r="C21" s="19" t="inlineStr">
         <is>
-          <t>Full account: 114 lines, 23 cost codes; section subsets verified (Natural Areas $116,963.24, Depots $23,626.58)</t>
+          <t>Full account: 121 lines, 23 cost codes; reconciled to SE2 26SLACT Accum Act p1-12 $268,032.19 to the cent (18-Jun-2026); supersedes prior $236,378.27 scope</t>
         </is>
       </c>
       <c r="D21" s="20" t="n">
-        <v>267532.19</v>
+        <v>268032.19</v>
       </c>
       <c r="E21" s="20" t="n">
-        <v>294285.41</v>
+        <v>294835.41</v>
       </c>
       <c r="F21" s="23" t="inlineStr">
         <is>
@@ -1816,17 +1816,17 @@
       </c>
       <c r="K21" s="19" t="inlineStr">
         <is>
-          <t>Reconciles to SE2 to the cent at the established scope ($236,378.27). 17-Jun-2026 evidence pass: 14 source invoices sighted exact to GL on the x1.1 test (Lockwise 2906937/2908705, TBM 97461/583/626/780, T2 3222869/3223786, Easy Signs 698933AU/713170AU, T&amp;H Levai INV-38877, 9016, Australasia 34828, 00735), all 8 distinct vendor ABN checksums PASS, GST math clean (no GST errors). Ausecology INV-4029 $8,480 + INV-4030 $6,360 sighted but $450 residual in GJ078960 and vendor ABN not on invoice (NARROWED). Evidence sighted now $208,815.65 of $236,378.27 (88.3%), $223,655.65 (94.6%) incl Ausecology narrowed. | 17-Jun MERGE: refreshed to 120 lines $267,532.19 (+6 P12 lines from the 17-Jun re-export, +$31,153.92) and 16 outstanding invoices sighted (+$66,404.23; Lothian, TBM, Ausecology, T2 Electrical, IDM, Radio Logan, Treescape, T&amp;H Levai, Wildlife Qld) - ported from PR-8. | 17-Jun: Materials Journal intake closed two more evidence gaps - EWN INV-14768 ($375.00) and Wallum 00059013 ($276.80) now SIGHTED. Four gaps remain: Provac INV-00037183 ($2,050, no source), Telstra Dec-25 ($727.95, intake scan image-only), Wallum 00031055/79/85/86 ($1,668) and 00060617/47 ($493.40).</t>
+          <t>Reconciles to SE2 to the cent at the established scope ($236,378.27). 17-Jun-2026 evidence pass: 14 source invoices sighted exact to GL on the x1.1 test (Lockwise 2906937/2908705, TBM 97461/583/626/780, T2 3222869/3223786, Easy Signs 698933AU/713170AU, T&amp;H Levai INV-38877, 9016, Australasia 34828, 00735), all 8 distinct vendor ABN checksums PASS, GST math clean (no GST errors). Ausecology INV-4029 $8,480 + INV-4030 $6,360 sighted but $450 residual in GJ078960 and vendor ABN not on invoice (NARROWED). Evidence sighted now $208,815.65 of $236,378.27 (88.3%), $223,655.65 (94.6%) incl Ausecology narrowed. | 17-Jun MERGE: refreshed to 120 lines $267,532.19 (+6 P12 lines from the 17-Jun re-export, +$31,153.92) and 16 outstanding invoices sighted (+$66,404.23; Lothian, TBM, Ausecology, T2 Electrical, IDM, Radio Logan, Treescape, T&amp;H Levai, Wildlife Qld) - ported from PR-8. | 17-Jun: Materials Journal intake closed two more evidence gaps - EWN INV-14768 ($375.00) and Wallum 00059013 ($276.80) now SIGHTED. Four gaps remain: Provac INV-00037183 ($2,050, no source), Telstra Dec-25 ($727.95, intake scan image-only), Wallum 00031055/79/85/86 ($1,668) and 00060617/47 ($493.40). | 18-Jun-2026: full export ties to SE2 enquiry $268,032.19 (121 lines) to the cent - scope reconciled UP from $236,378.27; the $31,653.92 was genuine P11/P12 activity, SE2-confirmed. Ausecology $450 residual CLOSED via GJ078960 Document Reconstruction (= EWN INV-14566 $75 + INV-14768 $375 legs in the same journal); EWN INV-14768 quantified $375. Wallum 00060617 ($319.60) and Barbs Trees 00031055 ($528.00) SIGHTED exact, ABN checksums PASS. PRINCE2 DOC0079602 confirmed a TWO-LIMB recode: 73211-&gt;73544 AND PK000082-&gt;PK000086 (Duen Jaemjamrat, svc 20141, off-home-PK miscode).</t>
         </is>
       </c>
       <c r="L21" s="19" t="inlineStr">
         <is>
-          <t>Residual evidence GAP (~$5,505 quantified + EWN): small series 00059013/00031055/79/85/86/00060617/47 ($2,438.20), Provac INV-00037183 ($2,050), Telstra Dec-25 ($727.95), EWN INV-14768 (amount tbc); Ausecology $450 residual + vendor ABN. SCOPE: fresh 17-Jun export totals $267,532.19 vs register $236,378.27, delta $31,153.92 (suspected added P11/P12 lines incl 8 Org Risk Consulting WHS invoices INV-250714/811-813/910-913 present in intake but absent from 73211 ledger refs) - reconcile before changing scope. F1-F7 and candidate rulings still Spero's.</t>
+          <t>Residual evidence GAP (~$5,505 quantified + EWN): small series 00059013/00031055/79/85/86/00060617/47 ($2,438.20), Provac INV-00037183 ($2,050), Telstra Dec-25 ($727.95), EWN INV-14768 (amount tbc); Ausecology $450 residual + vendor ABN. SCOPE: fresh 17-Jun export totals $267,532.19 vs register $236,378.27, delta $31,153.92 (suspected added P11/P12 lines incl 8 Org Risk Consulting WHS invoices INV-250714/811-813/910-913 present in intake but absent from 73211 ledger refs) - reconcile before changing scope. F1-F7 and candidate rulings still Spero's. | 18-Jun: NEW GAPs - 00001190 cemeteries standing order $500 (P12, PK000083, doc 1240297) and Destination Trails INV-0356 $24,340 (P12, above $20k floor, feeds F2). Small-series remainder now 00031079/85/86 + 00060647 ($1,313.80). Telstra Dec-25 already closed via Document Reconstruction 97; vendor PDF C00255407 now in _Sources_18-Jun-2026/ can upgrade it to a vendor sighting later.</t>
         </is>
       </c>
       <c r="M21" s="19" t="inlineStr">
         <is>
-          <t>02_NA73211_Minor_Contracts/ (verification record + 11-Jun + 17-Jun addenda; NA73211_Evidence/ 59 files; NA73211_Evidence_Manifest.csv; NA73211_EvidencePass_17-Jun-2026.csv)</t>
+          <t>02_NA73211_Minor_Contracts/ (verification record + 11/17/18-Jun addenda; NA73211_Evidence/ 63 files; NA73211_Evidence_Manifest.csv; NA73211_EvidencePass_17-Jun &amp; 18-Jun-2026.csv)</t>
         </is>
       </c>
       <c r="N21" s="19" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="O21" s="19" t="inlineStr">
         <is>
-          <t>17-Jun-2026 (intake disposition)</t>
+          <t>18-Jun-2026 (evidence pass)</t>
         </is>
       </c>
     </row>

--- a/00_Account_Review_Register.xlsx
+++ b/00_Account_Review_Register.xlsx
@@ -493,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="9" customWidth="1" style="14" min="1" max="1"/>
@@ -522,7 +522,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="23.25" customHeight="1" s="15">
       <c r="A4" s="18" t="inlineStr">
         <is>
@@ -2280,17 +2279,163 @@
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="15">
-      <c r="C28" s="26" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>73124</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>Full account: 28 lines; svc 20302 Parks Security Services holds $263,150.30</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>264132.36</v>
+      </c>
+      <c r="E28" s="14" t="n">
+        <v>290545.6</v>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="J28" s="14" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="K28" s="14" t="inlineStr">
+        <is>
+          <t>Coding-correct, NIL recode. Reconciles to SE2 to the cent ($264,132.36). L1/L2 GREEN: security correctly 73124 (dedicated NA; $27k/mo contract does not push to 73212 floor). Held AMBER on evidence only.</t>
+        </is>
+      </c>
+      <c r="L28" s="14" t="inlineStr">
+        <is>
+          <t>Sight the 25 security invoices + ~$24,600 credit note; confirm supplier ABN (checksum+ABR) and the Council security contract. No journal.</t>
+        </is>
+      </c>
+      <c r="M28" s="14" t="inlineStr">
+        <is>
+          <t>NA73124_Verification_Record.md; Ledger_73124_18-Jun-2026.xlsx</t>
+        </is>
+      </c>
+      <c r="N28" s="14" t="inlineStr">
+        <is>
+          <t>n/a (no recode)</t>
+        </is>
+      </c>
+      <c r="O28" s="14" t="inlineStr">
+        <is>
+          <t>18-Jun-2026 (4-limb pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>73535</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Tollway Charges</t>
+        </is>
+      </c>
+      <c r="C29" s="14" t="inlineStr">
+        <is>
+          <t>Full account: 587 lines, 12 toll accounts across 17 svc codes</t>
+        </is>
+      </c>
+      <c r="D29" s="14" t="n">
+        <v>46010.25</v>
+      </c>
+      <c r="E29" s="14" t="n">
+        <v>50611.28</v>
+      </c>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>GREEN</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="J29" s="14" t="inlineStr">
+        <is>
+          <t>AMBER</t>
+        </is>
+      </c>
+      <c r="K29" s="14" t="inlineStr">
+        <is>
+          <t>Coding-correct, NIL recode. Reconciles to SE2 to the cent ($46,010.25). L1/L2 GREEN: all toll-tag charges correctly 73535, attributed to the using section PK. Held AMBER on evidence only.</t>
+        </is>
+      </c>
+      <c r="L29" s="14" t="inlineStr">
+        <is>
+          <t>Sight the 12 Linkt/GoVia monthly statements; cross-check REGO list to the Parks fleet; confirm provider ABN/GST. No journal.</t>
+        </is>
+      </c>
+      <c r="M29" s="14" t="inlineStr">
+        <is>
+          <t>NA73535_Verification_Record.md; Ledger_73535_18-Jun-2026.xlsx</t>
+        </is>
+      </c>
+      <c r="N29" s="14" t="inlineStr">
+        <is>
+          <t>n/a (no recode)</t>
+        </is>
+      </c>
+      <c r="O29" s="14" t="inlineStr">
+        <is>
+          <t>18-Jun-2026 (4-limb pass)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" s="26" t="inlineStr">
         <is>
           <t>TOTAL reviewed $ (this register)</t>
         </is>
       </c>
-      <c r="D28" s="27">
-        <f>SUM(D5:D27)</f>
+      <c r="D30" s="27">
+        <f>SUM(D5:D29)</f>
         <v/>
       </c>
-      <c r="E28" s="27">
-        <f>SUM(E5:E27)</f>
+      <c r="E30" s="27">
+        <f>SUM(E5:E29)</f>
         <v/>
       </c>
     </row>

--- a/00_Account_Review_Register.xlsx
+++ b/00_Account_Review_Register.xlsx
@@ -1821,7 +1821,7 @@
       </c>
       <c r="L21" s="19" t="inlineStr">
         <is>
-          <t>Residual evidence GAP (~$5,505 quantified + EWN): small series 00059013/00031055/79/85/86/00060617/47 ($2,438.20), Provac INV-00037183 ($2,050), Telstra Dec-25 ($727.95), EWN INV-14768 (amount tbc); Ausecology $450 residual + vendor ABN. SCOPE: fresh 17-Jun export totals $267,532.19 vs register $236,378.27, delta $31,153.92 (suspected added P11/P12 lines incl 8 Org Risk Consulting WHS invoices INV-250714/811-813/910-913 present in intake but absent from 73211 ledger refs) - reconcile before changing scope. F1-F7 and candidate rulings still Spero's. | 18-Jun: NEW GAPs - 00001190 cemeteries standing order $500 (P12, PK000083, doc 1240297) and Destination Trails INV-0356 $24,340 (P12, above $20k floor, feeds F2). Small-series remainder now 00031079/85/86 + 00060647 ($1,313.80). Telstra Dec-25 already closed via Document Reconstruction 97; vendor PDF C00255407 now in _Sources_18-Jun-2026/ can upgrade it to a vendor sighting later.</t>
+          <t>Residual evidence GAP (~$5,505 quantified + EWN): small series 00059013/00031055/79/85/86/00060617/47 ($2,438.20), Provac INV-00037183 ($2,050), Telstra Dec-25 ($727.95), EWN INV-14768 (amount tbc); Ausecology $450 residual + vendor ABN. SCOPE: fresh 17-Jun export totals $267,532.19 vs register $236,378.27, delta $31,153.92 (suspected added P11/P12 lines incl 8 Org Risk Consulting WHS invoices INV-250714/811-813/910-913 present in intake but absent from 73211 ledger refs) - reconcile before changing scope. F1-F7 and candidate rulings still Spero's. | 18-Jun: NEW GAPs - 00001190 cemeteries standing order $500 (P12, PK000083, doc 1240297) and Destination Trails INV-0356 $24,340 (P12, above $20k floor, feeds F2). Small-series remainder now 00031079/85/86 + 00060647 ($1,313.80). Telstra Dec-25 already closed via Document Reconstruction 97; vendor PDF C00255407 now in _Sources_18-Jun-2026/ can upgrade it to a vendor sighting later. | 18-Jun pass 2: 15 Barbs/Wallum/RST small-series invoices SIGHTED exact (+$11,458.60), ABNs PASS; residual small-series 6 lines $3,133.70 (00059199/568/569, 00060647/756, 00061080) + Provac $2,050.</t>
         </is>
       </c>
       <c r="M21" s="19" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="O21" s="19" t="inlineStr">
         <is>
-          <t>18-Jun-2026 (evidence pass)</t>
+          <t>18-Jun-2026 (evidence pass 2)</t>
         </is>
       </c>
     </row>

--- a/00_Account_Review_Register.xlsx
+++ b/00_Account_Review_Register.xlsx
@@ -2113,12 +2113,12 @@
       </c>
       <c r="L25" s="19" t="inlineStr">
         <is>
-          <t>1 Sight the Trailbuilders registration backup for TE004922 ($642.14 combined) on the PCard reconciliation.</t>
+          <t>1 Sight the Trailbuilders registration backup for TE004922 ($642.14 combined) on the PCard reconciliation. | 18-Jun: TE004922 PTBA conference registration SIGHTED (Payment confirmation USD450=AUD626.48 + cover slip + email, Peter Salisnew; international, no AU GST/ABN). Evidence gap closed; $15.66 intl txn fee advisory.</t>
         </is>
       </c>
       <c r="M25" s="19" t="inlineStr">
         <is>
-          <t>06_NA73541_Conferences/NA73541_Notes_and_Kinatico_Intake.md (none sighted)</t>
+          <t>06_NA73541_Conferences/NA73541_Notes_and_Kinatico_Intake.md (none sighted); 06_NA73541_Conferences/NA73541_Evidence/ (PTBA set)</t>
         </is>
       </c>
       <c r="N25" s="19" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="O25" s="19" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>18-Jun-2026 (PTBA sighted)</t>
         </is>
       </c>
     </row>
